--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C25BF4FD-CBA3-4F6C-88EB-5301832C5180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025CE0C2-2400-4CDC-9205-0F92FDB6A7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1860" windowWidth="29040" windowHeight="18240" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,15 +32,16 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId17"/>
+    <externalReference r:id="rId18"/>
   </externalReferences>
   <definedNames>
     <definedName name="My_Named_Range">jestMiscTest!$A$8:$B$10</definedName>
     <definedName name="Table_Col_Named_Range">Table10[Col1]</definedName>
     <definedName name="Table_Named_Range">Table10[]</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="926" r:id="rId18"/>
+    <pivotCache cacheId="1" r:id="rId19"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1425,7 +1426,7 @@
     <numFmt numFmtId="168" formatCode="#,##0&quot; EUR €&quot;"/>
     <numFmt numFmtId="169" formatCode="&quot;€&quot;#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2160,7 +2161,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2357,10 +2358,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2373,7 +2374,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2381,157 +2381,6 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1493241F-B85D-4F84-BBA0-86191B8FD032}"/>
   </cellStyles>
   <dxfs count="47">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike/>
-        <u/>
-        <color theme="7"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="lightTrellis">
-          <fgColor theme="4"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2949,6 +2798,157 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike/>
+        <u/>
+        <color theme="7"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="4"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
@@ -3970,6 +3970,514 @@
 </file>
 
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2200"/>
+              <a:t>chart with composite ranges</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>([2]Sheet1!$A$27:$C$35,[2]Sheet1!$A$27:$C$31)</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>24</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>27</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>45</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>17</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>43</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>11</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>16</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>24</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>27</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>45</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>48</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>45</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>25</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>31</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>20</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>19</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>16</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>48</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>45</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>25</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Emily Anderson (Emmy)</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Sophie Allen (Saffi)</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Chloe Adams</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Megan Alexander (Meg)</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lucy Arnold (Lulu)</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Hannah Alvarez</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Jessica Alcock (Jess)</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Charlotte Anaya</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lauren Anthony</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Emily Anderson (Emmy)</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Sophie Allen (Saffi)</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Chloe Adams</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Megan Alexander (Meg)</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lucy Arnold (Lulu)</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[2]Sheet1!$B$27:$B$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="7030A0"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0BF8-4BDD-A213-D4207D685044}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C65911"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="C65911"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>[2]Sheet1!$A$27:$A$31</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[2]Sheet1!$C$27:$C$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="C65911"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0BF8-4BDD-A213-D4207D685044}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="70"/>
+        <c:overlap val="-20"/>
+        <c:axId val="17781237"/>
+        <c:axId val="88853993"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="17781237"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="1000" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="88853993"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="88853993"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="1000" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="17781237"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr sz="1000" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln cmpd="sng">
+      <a:solidFill>
+        <a:srgbClr val="000000"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8653,6 +9161,47 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Chart 11" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42D23678-8AAB-414A-8704-0FA4F2260912}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8796,6 +9345,149 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Formulas"/>
+      <sheetName val="jestSheet"/>
+      <sheetName val="jestStyles"/>
+      <sheetName val="jestCfs"/>
+      <sheetName val="jestTable"/>
+      <sheetName val="jestPivot"/>
+      <sheetName val="jestCharts"/>
+      <sheetName val="jestMiscTest"/>
+      <sheetName val="jestHiddenSheet"/>
+      <sheetName val="jestFreezePane"/>
+      <sheetName val="jestImages"/>
+      <sheetName val="jestOneCellAnchor"/>
+      <sheetName val="jestDataValidations"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="27">
+          <cell r="A27" t="str">
+            <v>Emily Anderson (Emmy)</v>
+          </cell>
+          <cell r="B27">
+            <v>12</v>
+          </cell>
+          <cell r="C27">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28" t="str">
+            <v>Sophie Allen (Saffi)</v>
+          </cell>
+          <cell r="B28">
+            <v>48</v>
+          </cell>
+          <cell r="C28">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29" t="str">
+            <v>Chloe Adams</v>
+          </cell>
+          <cell r="B29">
+            <v>45</v>
+          </cell>
+          <cell r="C29">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>Megan Alexander (Meg)</v>
+          </cell>
+          <cell r="B30">
+            <v>1</v>
+          </cell>
+          <cell r="C30">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31" t="str">
+            <v>Lucy Arnold (Lulu)</v>
+          </cell>
+          <cell r="B31">
+            <v>25</v>
+          </cell>
+          <cell r="C31">
+            <v>45</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32" t="str">
+            <v>Hannah Alvarez</v>
+          </cell>
+          <cell r="B32">
+            <v>31</v>
+          </cell>
+          <cell r="C32">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33" t="str">
+            <v>Jessica Alcock (Jess)</v>
+          </cell>
+          <cell r="B33">
+            <v>20</v>
+          </cell>
+          <cell r="C33">
+            <v>43</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34" t="str">
+            <v>Charlotte Anaya</v>
+          </cell>
+          <cell r="B34">
+            <v>19</v>
+          </cell>
+          <cell r="C34">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35" t="str">
+            <v>Lauren Anthony</v>
+          </cell>
+          <cell r="B35">
+            <v>16</v>
+          </cell>
+          <cell r="C35">
+            <v>16</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Adrien" refreshedDate="44606.425659606481" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="8" xr:uid="{F88877D8-4C71-40F4-AB33-E2E5CAE6E797}">
   <cacheSource type="worksheet">
@@ -8848,6 +9540,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
+    </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -8915,7 +9610,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="926" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -9065,7 +9760,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="44" dataDxfId="43">
   <autoFilter ref="C3:J5" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9077,22 +9772,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="14" totalsRowDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="9">
+    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="38" totalsRowDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="35">
       <calculatedColumnFormula>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="7">
+    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="33">
       <calculatedColumnFormula>SUM(Table3[Rank])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="5">
+    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31">
       <calculatedColumnFormula>SUM(Table3[[#All],[Rank]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="2" totalsRowDxfId="3">
+    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="29">
       <calculatedColumnFormula>Table3[[#Totals],[Rank]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="0" totalsRowDxfId="1">
+    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="27">
       <calculatedColumnFormula>Table3[[#Headers],[Rank]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9213,9 +9908,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9253,7 +9948,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -9359,7 +10054,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9501,7 +10196,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -9513,7 +10208,7 @@
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.140625" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
@@ -9522,156 +10217,103 @@
     <col min="6" max="26" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" customHeight="1">
+    <row r="1" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="21"/>
-      <c r="B1" s="110"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
       <c r="G1" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-    </row>
-    <row r="2" spans="1:12" ht="27.75">
-      <c r="A2" s="110"/>
+    </row>
+    <row r="2" spans="1:12" ht="27.75" x14ac:dyDescent="0.2">
       <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
       <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G2" s="109">
         <v>5</v>
       </c>
-      <c r="H2" s="111" t="s">
+      <c r="H2" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="116"/>
-      <c r="J2" s="110"/>
+      <c r="I2" s="111"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="110"/>
-    </row>
-    <row r="3" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A3" s="110"/>
-      <c r="B3" s="110"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
+    </row>
+    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="109">
         <v>8</v>
       </c>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
       <c r="J3" s="5"/>
       <c r="K3" s="112">
         <v>5</v>
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A4" s="110"/>
+    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="109">
         <v>12.4</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
       <c r="F4" s="8" t="s">
         <v>7</v>
       </c>
       <c r="G4" s="109">
         <v>9</v>
       </c>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
       <c r="J4" s="5"/>
       <c r="K4" s="113"/>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A5" s="110"/>
-      <c r="B5" s="110"/>
+    <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="109">
         <v>42</v>
       </c>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
       <c r="G5" s="109">
         <v>15</v>
       </c>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="111"/>
       <c r="J5" s="5"/>
       <c r="K5" s="113"/>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A6" s="110"/>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
+    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G6" s="109">
         <v>22</v>
       </c>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
       <c r="J6" s="5"/>
       <c r="K6" s="113"/>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A7" s="110"/>
-      <c r="B7" s="110"/>
+    <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="109">
         <v>3</v>
       </c>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="110"/>
       <c r="J7" s="5"/>
       <c r="K7" s="113"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
+    <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G8" s="109">
         <v>30</v>
       </c>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
       <c r="J8" s="5"/>
       <c r="K8" s="114"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A9" s="110"/>
+    <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
@@ -9679,19 +10321,9 @@
         <f>SUM(C4:C5)</f>
         <v>54.4</v>
       </c>
-      <c r="D9" s="110"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="110"/>
       <c r="K9" s="10"/>
-      <c r="L9" s="110"/>
-    </row>
-    <row r="10" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A10" s="110"/>
-      <c r="B10" s="110"/>
+    </row>
+    <row r="10" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="109">
         <f>SUM(C4:C7)</f>
         <v>57.4</v>
@@ -9699,35 +10331,14 @@
       <c r="D10" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="110"/>
-    </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A11" s="110"/>
-      <c r="B11" s="110"/>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="109">
         <f>-(3+C7*SUM(C4:C7))</f>
         <v>-175.2</v>
       </c>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="110"/>
-      <c r="K11" s="110"/>
-      <c r="L11" s="110"/>
-    </row>
-    <row r="12" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A12" s="110"/>
-      <c r="B12" s="110"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="109">
         <f>SUM(C9:C11)</f>
         <v>-63.399999999999991</v>
@@ -9735,34 +10346,14 @@
       <c r="D12" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="110"/>
-      <c r="F12" s="110"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="110"/>
-      <c r="K12" s="110"/>
-      <c r="L12" s="110"/>
-    </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A13" s="110"/>
-      <c r="B13" s="110"/>
-      <c r="C13" s="110"/>
-      <c r="D13" s="110"/>
-      <c r="E13" s="110"/>
-      <c r="F13" s="110"/>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G13" s="109">
         <f>A1+A2+A3+A4+A5+A6+A7+A8+A9+A10+A11+A12+A13+A14+A15+A16+A17+A18</f>
         <v>0</v>
       </c>
-      <c r="H13" s="110"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="110"/>
-      <c r="K13" s="110"/>
-      <c r="L13" s="110"/>
-    </row>
-    <row r="14" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A14" s="110"/>
+    </row>
+    <row r="14" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
@@ -9770,93 +10361,37 @@
         <f ca="1">C14</f>
         <v>#CYCLE</v>
       </c>
-      <c r="D14" s="110"/>
-      <c r="E14" s="110"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="110"/>
-      <c r="L14" s="110"/>
-    </row>
-    <row r="15" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A15" s="110"/>
-      <c r="B15" s="110"/>
+    </row>
+    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="110"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
-      <c r="I15" s="110"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="110"/>
-    </row>
-    <row r="16" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A16" s="110"/>
-      <c r="B16" s="110"/>
+    </row>
+    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" s="109" t="str">
         <f>C15</f>
         <v>=(+</v>
       </c>
-      <c r="D16" s="110"/>
-      <c r="E16" s="110"/>
-      <c r="F16" s="110"/>
-      <c r="G16" s="110"/>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110"/>
-      <c r="J16" s="110"/>
-      <c r="K16" s="110"/>
-      <c r="L16" s="110"/>
-    </row>
-    <row r="17" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A17" s="110"/>
-      <c r="B17" s="110"/>
+    </row>
+    <row r="17" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="109" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="110"/>
-      <c r="E17" s="110"/>
-      <c r="F17" s="110"/>
-      <c r="G17" s="110"/>
-      <c r="H17" s="110"/>
-      <c r="I17" s="110"/>
-    </row>
-    <row r="18" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A18" s="110"/>
-      <c r="B18" s="110"/>
+    </row>
+    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="110"/>
-      <c r="E18" s="110"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="110"/>
-    </row>
-    <row r="19" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="110"/>
+    </row>
+    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E19" s="3"/>
-      <c r="F19" s="110"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-    </row>
-    <row r="20" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A20" s="110"/>
+    </row>
+    <row r="20" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="5"/>
       <c r="C20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="110"/>
       <c r="E20" s="10" t="s">
         <v>16</v>
       </c>
@@ -9865,9 +10400,8 @@
         <v>17</v>
       </c>
       <c r="H20" s="6"/>
-      <c r="I20" s="110"/>
-    </row>
-    <row r="21" spans="1:9" ht="17.25" customHeight="1">
+    </row>
+    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
         <v>18</v>
       </c>
@@ -9875,26 +10409,15 @@
         <f>jestCharts!B2</f>
         <v>0</v>
       </c>
-      <c r="C21" s="110"/>
-      <c r="D21" s="110"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="110"/>
       <c r="G21" s="10"/>
-      <c r="H21" s="110"/>
-      <c r="I21" s="110"/>
-    </row>
-    <row r="23" spans="1:9" ht="17.25" customHeight="1">
+    </row>
+    <row r="23" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="110"/>
       <c r="C23" s="15">
         <v>0.43</v>
       </c>
-      <c r="D23" s="110"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="110"/>
-      <c r="G23" s="110"/>
       <c r="H23" s="109">
         <v>0</v>
       </c>
@@ -9902,16 +10425,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A24" s="110"/>
-      <c r="B24" s="110"/>
+    <row r="24" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="16">
         <v>10</v>
       </c>
-      <c r="D24" s="110"/>
-      <c r="E24" s="110"/>
-      <c r="F24" s="110"/>
-      <c r="G24" s="110"/>
       <c r="H24" s="109">
         <v>1</v>
       </c>
@@ -9919,16 +10436,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A25" s="110"/>
-      <c r="B25" s="110"/>
+    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="16">
         <v>10.122999999999999</v>
       </c>
-      <c r="D25" s="110"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="110"/>
-      <c r="G25" s="110"/>
       <c r="H25" s="109">
         <v>2</v>
       </c>
@@ -9936,18 +10447,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A26" s="110"/>
+    <row r="26" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="109" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="110"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="110"/>
-      <c r="G26" s="110"/>
       <c r="H26" s="109">
         <v>3</v>
       </c>
@@ -9955,7 +10461,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17.25" customHeight="1">
+    <row r="27" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="109" t="s">
         <v>22</v>
       </c>
@@ -9965,10 +10471,6 @@
       <c r="C27" s="109">
         <v>24</v>
       </c>
-      <c r="D27" s="110"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="110"/>
-      <c r="G27" s="110"/>
       <c r="H27" s="109">
         <v>4</v>
       </c>
@@ -9976,7 +10478,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17.25" customHeight="1">
+    <row r="28" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="109" t="s">
         <v>23</v>
       </c>
@@ -9986,10 +10488,6 @@
       <c r="C28" s="109">
         <v>12</v>
       </c>
-      <c r="D28" s="110"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="110"/>
-      <c r="G28" s="110"/>
       <c r="H28" s="109">
         <v>5</v>
       </c>
@@ -9997,7 +10495,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17.25" customHeight="1">
+    <row r="29" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="109" t="s">
         <v>24</v>
       </c>
@@ -10007,10 +10505,6 @@
       <c r="C29" s="109">
         <v>27</v>
       </c>
-      <c r="D29" s="110"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="110"/>
-      <c r="G29" s="110"/>
       <c r="H29" s="109">
         <v>6</v>
       </c>
@@ -10018,7 +10512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17.25" customHeight="1">
+    <row r="30" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="109" t="s">
         <v>25</v>
       </c>
@@ -10028,10 +10522,6 @@
       <c r="C30" s="109">
         <v>9</v>
       </c>
-      <c r="D30" s="110"/>
-      <c r="E30" s="110"/>
-      <c r="F30" s="110"/>
-      <c r="G30" s="110"/>
       <c r="H30" s="109">
         <v>7</v>
       </c>
@@ -10039,7 +10529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17.25" customHeight="1">
+    <row r="31" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="109" t="s">
         <v>26</v>
       </c>
@@ -10049,10 +10539,6 @@
       <c r="C31" s="109">
         <v>45</v>
       </c>
-      <c r="D31" s="110"/>
-      <c r="E31" s="110"/>
-      <c r="F31" s="110"/>
-      <c r="G31" s="110"/>
       <c r="H31" s="109">
         <v>8</v>
       </c>
@@ -10060,7 +10546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17.25" customHeight="1">
+    <row r="32" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="109" t="s">
         <v>27</v>
       </c>
@@ -10070,10 +10556,6 @@
       <c r="C32" s="109">
         <v>17</v>
       </c>
-      <c r="D32" s="110"/>
-      <c r="E32" s="110"/>
-      <c r="F32" s="110"/>
-      <c r="G32" s="110"/>
       <c r="H32" s="109">
         <v>9</v>
       </c>
@@ -10081,7 +10563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17.25" customHeight="1">
+    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="109" t="s">
         <v>28</v>
       </c>
@@ -10091,10 +10573,6 @@
       <c r="C33" s="109">
         <v>43</v>
       </c>
-      <c r="D33" s="110"/>
-      <c r="E33" s="110"/>
-      <c r="F33" s="110"/>
-      <c r="G33" s="110"/>
       <c r="H33" s="109">
         <v>10</v>
       </c>
@@ -10102,7 +10580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17.25" customHeight="1">
+    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="109" t="s">
         <v>29</v>
       </c>
@@ -10112,14 +10590,8 @@
       <c r="C34" s="109">
         <v>11</v>
       </c>
-      <c r="D34" s="110"/>
-      <c r="E34" s="110"/>
-      <c r="F34" s="110"/>
-      <c r="G34" s="110"/>
-      <c r="H34" s="110"/>
-      <c r="I34" s="110"/>
-    </row>
-    <row r="35" spans="1:9" ht="17.25" customHeight="1">
+    </row>
+    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="109" t="s">
         <v>30</v>
       </c>
@@ -10129,12 +10601,6 @@
       <c r="C35" s="109">
         <v>16</v>
       </c>
-      <c r="D35" s="110"/>
-      <c r="E35" s="110"/>
-      <c r="F35" s="110"/>
-      <c r="G35" s="110"/>
-      <c r="H35" s="110"/>
-      <c r="I35" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10142,7 +10608,7 @@
     <mergeCell ref="K3:K8"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C100 B21">
-    <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>42</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10187,7 +10653,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10196,7 +10662,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10205,7 +10671,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.85546875" customWidth="1"/>
@@ -10222,7 +10688,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -10232,7 +10698,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025F2510-D243-4DA1-81DE-BBDDA9BC3681}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="4" width="14.140625" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" customWidth="1"/>
@@ -10242,7 +10708,7 @@
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="105" t="s">
         <v>424</v>
       </c>
@@ -10274,17 +10740,17 @@
         <v>433</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="110">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>4</v>
       </c>
-      <c r="B2" s="110">
+      <c r="B2">
         <v>99.5</v>
       </c>
-      <c r="C2" s="110">
-        <v>1</v>
-      </c>
-      <c r="D2" s="110" t="s">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>434</v>
       </c>
       <c r="E2" s="39">
@@ -10299,24 +10765,24 @@
       <c r="H2" s="39">
         <v>45292</v>
       </c>
-      <c r="I2" s="110">
+      <c r="I2">
         <v>4</v>
       </c>
-      <c r="J2" s="110">
+      <c r="J2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="110">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3" s="110">
+      <c r="B3">
         <v>40</v>
       </c>
-      <c r="C3" s="110">
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" s="110" t="s">
+      <c r="D3" t="s">
         <v>436</v>
       </c>
       <c r="E3" s="39">
@@ -10331,24 +10797,24 @@
       <c r="H3" s="39">
         <v>45231</v>
       </c>
-      <c r="I3" s="110" t="s">
+      <c r="I3" t="s">
         <v>435</v>
       </c>
-      <c r="J3" s="110">
+      <c r="J3">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="110">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>9</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" s="110">
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" s="110" t="s">
+      <c r="D4" t="s">
         <v>438</v>
       </c>
       <c r="E4" s="39">
@@ -10363,24 +10829,24 @@
       <c r="H4" s="39">
         <v>45325</v>
       </c>
-      <c r="I4" s="110">
+      <c r="I4">
         <v>3</v>
       </c>
-      <c r="J4" s="110">
+      <c r="J4">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="110">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5">
         <v>120</v>
       </c>
-      <c r="C5" s="110">
+      <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" s="110" t="s">
+      <c r="D5" t="s">
         <v>436</v>
       </c>
       <c r="E5" s="39">
@@ -10389,30 +10855,30 @@
       <c r="F5" s="108">
         <v>0.66666666666666663</v>
       </c>
-      <c r="G5" s="110" t="s">
+      <c r="G5" t="s">
         <v>440</v>
       </c>
       <c r="H5" s="39">
         <v>45084</v>
       </c>
-      <c r="I5" s="110">
+      <c r="I5">
         <v>3</v>
       </c>
-      <c r="J5" s="110">
+      <c r="J5">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="110">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>7</v>
       </c>
-      <c r="B6" s="110">
+      <c r="B6">
         <v>12</v>
       </c>
-      <c r="C6" s="110">
+      <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" s="110" t="s">
+      <c r="D6" t="s">
         <v>438</v>
       </c>
       <c r="E6" s="39">
@@ -10421,16 +10887,16 @@
       <c r="F6" s="108">
         <v>0.5229166666666667</v>
       </c>
-      <c r="G6" s="110" t="s">
+      <c r="G6" t="s">
         <v>441</v>
       </c>
       <c r="H6" s="39">
         <v>45420</v>
       </c>
-      <c r="I6" s="110" t="s">
+      <c r="I6" t="s">
         <v>440</v>
       </c>
-      <c r="J6" s="110">
+      <c r="J6">
         <v>15</v>
       </c>
     </row>
@@ -10479,7 +10945,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{175FB5D6-D3ED-FD4F-886B-71BD0CB28755}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10489,7 +10955,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B936FE7B-5147-E945-A711-7FBABD0575D3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10502,12 +10968,12 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:R163"/>
-  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="26" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17.25" customHeight="1">
+    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="109" t="s">
         <v>31</v>
       </c>
@@ -10520,8 +10986,6 @@
       <c r="D1" s="109" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
       <c r="G1" s="17" t="s">
         <v>35</v>
       </c>
@@ -10537,19 +11001,14 @@
       <c r="K1" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
       <c r="N1" s="109">
         <v>0.1</v>
       </c>
-      <c r="O1" s="110"/>
       <c r="P1" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-    </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1">
+    </row>
+    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="109" t="s">
         <v>41</v>
       </c>
@@ -10564,8 +11023,6 @@
         <f t="shared" ref="D2:D33" si="0">IF(B2=C2,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
       <c r="G2" s="109" t="s">
         <v>42</v>
       </c>
@@ -10581,26 +11038,23 @@
       <c r="K2" s="109">
         <v>5</v>
       </c>
-      <c r="L2" s="110"/>
-      <c r="M2" s="110"/>
       <c r="N2" s="109">
         <v>0.2</v>
       </c>
-      <c r="O2" s="110"/>
-      <c r="P2" s="110">
+      <c r="P2">
         <f>SUM(H2, I$2)</f>
         <v>1230.7</v>
       </c>
-      <c r="Q2" s="110">
+      <c r="Q2">
         <f>SUM(H2, $I2)</f>
         <v>1230.7</v>
       </c>
-      <c r="R2" s="110">
+      <c r="R2">
         <f>SUM(H2, $I$2)</f>
         <v>1230.7</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17.25" customHeight="1">
+    <row r="3" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="109" t="s">
         <v>43</v>
       </c>
@@ -10615,8 +11069,6 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
       <c r="G3" s="109" t="s">
         <v>44</v>
       </c>
@@ -10632,26 +11084,23 @@
       <c r="K3" s="109">
         <v>7</v>
       </c>
-      <c r="L3" s="110"/>
-      <c r="M3" s="110"/>
       <c r="N3" s="109">
         <v>0.4</v>
       </c>
-      <c r="O3" s="110"/>
-      <c r="P3" s="110">
+      <c r="P3">
         <f t="shared" ref="P3:P6" si="1">SUM(H3, I$2)</f>
         <v>1217.7</v>
       </c>
-      <c r="Q3" s="110">
+      <c r="Q3">
         <f t="shared" ref="Q3:Q6" si="2">SUM(H3, $I3)</f>
         <v>513.9</v>
       </c>
-      <c r="R3" s="110">
+      <c r="R3">
         <f t="shared" ref="R3:R6" si="3">SUM(H3, $I$2)</f>
         <v>1217.7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="17.25" customHeight="1">
+    <row r="4" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="109" t="s">
         <v>45</v>
       </c>
@@ -10666,8 +11115,6 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
       <c r="G4" s="109" t="s">
         <v>46</v>
       </c>
@@ -10683,26 +11130,23 @@
       <c r="K4" s="109">
         <v>3</v>
       </c>
-      <c r="L4" s="110"/>
-      <c r="M4" s="110"/>
       <c r="N4" s="109">
         <v>0.5</v>
       </c>
-      <c r="O4" s="110"/>
-      <c r="P4" s="110">
+      <c r="P4">
         <f t="shared" si="1"/>
         <v>1230.7</v>
       </c>
-      <c r="Q4" s="110">
+      <c r="Q4">
         <f t="shared" si="2"/>
         <v>278.39999999999998</v>
       </c>
-      <c r="R4" s="110">
+      <c r="R4">
         <f t="shared" si="3"/>
         <v>1230.7</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="17.25" customHeight="1">
+    <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="109" t="s">
         <v>47</v>
       </c>
@@ -10717,8 +11161,6 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
       <c r="G5" s="109" t="s">
         <v>48</v>
       </c>
@@ -10734,26 +11176,23 @@
       <c r="K5" s="109">
         <v>4</v>
       </c>
-      <c r="L5" s="110"/>
-      <c r="M5" s="110"/>
       <c r="N5" s="109">
         <v>0.6</v>
       </c>
-      <c r="O5" s="110"/>
-      <c r="P5" s="110">
+      <c r="P5">
         <f t="shared" si="1"/>
         <v>1246.7</v>
       </c>
-      <c r="Q5" s="110">
+      <c r="Q5">
         <f t="shared" si="2"/>
         <v>4743.3</v>
       </c>
-      <c r="R5" s="110">
+      <c r="R5">
         <f t="shared" si="3"/>
         <v>1246.7</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="17.25" customHeight="1">
+    <row r="6" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="109" t="s">
         <v>49</v>
       </c>
@@ -10768,8 +11207,6 @@
         <f>IF(B6=C6,1,0)</f>
         <v>1</v>
       </c>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
       <c r="G6" s="109" t="s">
         <v>50</v>
       </c>
@@ -10785,26 +11222,23 @@
       <c r="K6" s="109">
         <v>1000</v>
       </c>
-      <c r="L6" s="110"/>
-      <c r="M6" s="110"/>
       <c r="N6" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="O6" s="110"/>
-      <c r="P6" s="110">
+      <c r="P6">
         <f t="shared" si="1"/>
         <v>1213.7</v>
       </c>
-      <c r="Q6" s="110">
+      <c r="Q6">
         <f t="shared" si="2"/>
         <v>21.1</v>
       </c>
-      <c r="R6" s="110">
+      <c r="R6">
         <f t="shared" si="3"/>
         <v>1213.7</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.25" customHeight="1">
+    <row r="7" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="109" t="s">
         <v>52</v>
       </c>
@@ -10819,8 +11253,6 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E7" s="110"/>
-      <c r="F7" s="110"/>
       <c r="G7" s="109" t="s">
         <v>53</v>
       </c>
@@ -10836,17 +11268,11 @@
       <c r="K7" s="109">
         <v>2</v>
       </c>
-      <c r="L7" s="110"/>
-      <c r="M7" s="110"/>
       <c r="N7" s="109" t="b">
         <v>1</v>
       </c>
-      <c r="O7" s="110"/>
-      <c r="P7" s="110"/>
-      <c r="Q7" s="110"/>
-      <c r="R7" s="110"/>
-    </row>
-    <row r="8" spans="1:18" ht="17.25" customHeight="1">
+    </row>
+    <row r="8" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="109" t="s">
         <v>54</v>
       </c>
@@ -10861,8 +11287,6 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
       <c r="G8" s="109" t="s">
         <v>55</v>
       </c>
@@ -10878,17 +11302,11 @@
       <c r="K8" s="109">
         <v>1</v>
       </c>
-      <c r="L8" s="110"/>
-      <c r="M8" s="110"/>
       <c r="N8" s="109" t="b">
         <v>0</v>
       </c>
-      <c r="O8" s="110"/>
-      <c r="P8" s="110"/>
-      <c r="Q8" s="110"/>
-      <c r="R8" s="110"/>
-    </row>
-    <row r="9" spans="1:18" ht="17.25" customHeight="1">
+    </row>
+    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="109" t="s">
         <v>56</v>
       </c>
@@ -10903,8 +11321,6 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
       <c r="G9" s="109" t="s">
         <v>57</v>
       </c>
@@ -10920,15 +11336,8 @@
       <c r="K9" s="109">
         <v>30</v>
       </c>
-      <c r="L9" s="110"/>
-      <c r="M9" s="110"/>
-      <c r="N9" s="110"/>
-      <c r="O9" s="110"/>
-      <c r="P9" s="110"/>
-      <c r="Q9" s="110"/>
-      <c r="R9" s="110"/>
-    </row>
-    <row r="10" spans="1:18" ht="17.25" customHeight="1">
+    </row>
+    <row r="10" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="109" t="s">
         <v>58</v>
       </c>
@@ -10943,22 +11352,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="110"/>
-      <c r="M10" s="110"/>
-      <c r="N10" s="110"/>
-      <c r="O10" s="110"/>
-      <c r="P10" s="110"/>
-      <c r="Q10" s="110"/>
-      <c r="R10" s="110"/>
-    </row>
-    <row r="11" spans="1:18" ht="17.25" customHeight="1">
+    </row>
+    <row r="11" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="109" t="s">
         <v>59</v>
       </c>
@@ -10973,24 +11368,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
       <c r="G11" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="110"/>
-      <c r="K11" s="110"/>
-      <c r="L11" s="110"/>
-      <c r="M11" s="110"/>
-      <c r="N11" s="110"/>
-      <c r="O11" s="110"/>
-      <c r="P11" s="110"/>
-      <c r="Q11" s="110"/>
-      <c r="R11" s="110"/>
-    </row>
-    <row r="12" spans="1:18" ht="17.25" customHeight="1">
+    </row>
+    <row r="12" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="109" t="s">
         <v>61</v>
       </c>
@@ -11005,8 +11387,6 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E12" s="110"/>
-      <c r="F12" s="110"/>
       <c r="G12" s="17" t="s">
         <v>35</v>
       </c>
@@ -11022,15 +11402,8 @@
       <c r="K12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="L12" s="110"/>
-      <c r="M12" s="110"/>
-      <c r="N12" s="110"/>
-      <c r="O12" s="110"/>
-      <c r="P12" s="110"/>
-      <c r="Q12" s="110"/>
-      <c r="R12" s="110"/>
-    </row>
-    <row r="13" spans="1:18" ht="17.25" customHeight="1">
+    </row>
+    <row r="13" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="109" t="s">
         <v>62</v>
       </c>
@@ -11045,8 +11418,6 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E13" s="110"/>
-      <c r="F13" s="110"/>
       <c r="G13" s="109" t="s">
         <v>46</v>
       </c>
@@ -11062,15 +11433,8 @@
       <c r="K13" s="109" t="s">
         <v>66</v>
       </c>
-      <c r="L13" s="110"/>
-      <c r="M13" s="110"/>
-      <c r="N13" s="110"/>
-      <c r="O13" s="110"/>
-      <c r="P13" s="110"/>
-      <c r="Q13" s="110"/>
-      <c r="R13" s="110"/>
-    </row>
-    <row r="14" spans="1:18" ht="17.25" customHeight="1">
+    </row>
+    <row r="14" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="109" t="s">
         <v>67</v>
       </c>
@@ -11085,22 +11449,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E14" s="110"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="110"/>
-      <c r="L14" s="110"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="110"/>
-      <c r="O14" s="110"/>
-      <c r="P14" s="110"/>
-      <c r="Q14" s="110"/>
-      <c r="R14" s="110"/>
-    </row>
-    <row r="15" spans="1:18" ht="17.25" customHeight="1">
+    </row>
+    <row r="15" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="109" t="s">
         <v>68</v>
       </c>
@@ -11115,22 +11465,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E15" s="110"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
-      <c r="I15" s="110"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="110"/>
-      <c r="M15" s="110"/>
-      <c r="N15" s="110"/>
-      <c r="O15" s="110"/>
-      <c r="P15" s="110"/>
-      <c r="Q15" s="110"/>
-      <c r="R15" s="110"/>
-    </row>
-    <row r="16" spans="1:18" ht="17.25" customHeight="1">
+    </row>
+    <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="109" t="s">
         <v>69</v>
       </c>
@@ -11145,22 +11481,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E16" s="110"/>
-      <c r="F16" s="110"/>
-      <c r="G16" s="110"/>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110"/>
-      <c r="J16" s="110"/>
-      <c r="K16" s="110"/>
-      <c r="L16" s="110"/>
-      <c r="M16" s="110"/>
-      <c r="N16" s="110"/>
-      <c r="O16" s="110"/>
-      <c r="P16" s="110"/>
-      <c r="Q16" s="110"/>
-      <c r="R16" s="110"/>
-    </row>
-    <row r="17" spans="1:4" ht="17.25" customHeight="1">
+    </row>
+    <row r="17" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="109" t="s">
         <v>70</v>
       </c>
@@ -11176,7 +11498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="17.25" customHeight="1">
+    <row r="18" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="109" t="s">
         <v>71</v>
       </c>
@@ -11192,7 +11514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="17.25" customHeight="1">
+    <row r="19" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="109" t="s">
         <v>72</v>
       </c>
@@ -11208,7 +11530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="17.25" customHeight="1">
+    <row r="20" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="109" t="s">
         <v>73</v>
       </c>
@@ -11224,7 +11546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="17.25" customHeight="1">
+    <row r="21" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="109" t="s">
         <v>74</v>
       </c>
@@ -11240,7 +11562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17.25" customHeight="1">
+    <row r="22" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="109" t="s">
         <v>76</v>
       </c>
@@ -11256,7 +11578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="17.25" customHeight="1">
+    <row r="23" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="109" t="s">
         <v>77</v>
       </c>
@@ -11272,7 +11594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="17.25" customHeight="1">
+    <row r="24" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="109" t="s">
         <v>78</v>
       </c>
@@ -11289,7 +11611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="17.25" customHeight="1">
+    <row r="25" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="109" t="s">
         <v>79</v>
       </c>
@@ -11305,7 +11627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="17.25" customHeight="1">
+    <row r="26" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="109" t="s">
         <v>81</v>
       </c>
@@ -11321,7 +11643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="17.25" customHeight="1">
+    <row r="27" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="109" t="s">
         <v>82</v>
       </c>
@@ -11337,7 +11659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="17.25" customHeight="1">
+    <row r="28" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="109" t="s">
         <v>83</v>
       </c>
@@ -11354,7 +11676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="17.25" customHeight="1">
+    <row r="29" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="109" t="s">
         <v>84</v>
       </c>
@@ -11370,7 +11692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="17.25" customHeight="1">
+    <row r="30" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="109" t="s">
         <v>85</v>
       </c>
@@ -11386,7 +11708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="17.25" customHeight="1">
+    <row r="31" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="109" t="s">
         <v>86</v>
       </c>
@@ -11402,7 +11724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="17.25" customHeight="1">
+    <row r="32" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="109" t="s">
         <v>87</v>
       </c>
@@ -11418,7 +11740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="17.25" customHeight="1">
+    <row r="33" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="109" t="s">
         <v>88</v>
       </c>
@@ -11434,7 +11756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="17.25" customHeight="1">
+    <row r="34" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="109" t="s">
         <v>89</v>
       </c>
@@ -11450,7 +11772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="17.25" customHeight="1">
+    <row r="35" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="109" t="s">
         <v>90</v>
       </c>
@@ -11466,7 +11788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="17.25" customHeight="1">
+    <row r="36" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="109" t="s">
         <v>91</v>
       </c>
@@ -11482,7 +11804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="17.25" customHeight="1">
+    <row r="37" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="109" t="s">
         <v>92</v>
       </c>
@@ -11498,7 +11820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="17.25" customHeight="1">
+    <row r="38" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="109" t="s">
         <v>93</v>
       </c>
@@ -11515,7 +11837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="17.25" customHeight="1">
+    <row r="39" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="109" t="s">
         <v>94</v>
       </c>
@@ -11531,7 +11853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="17.25" customHeight="1">
+    <row r="40" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="109" t="s">
         <v>95</v>
       </c>
@@ -11547,7 +11869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="17.25" customHeight="1">
+    <row r="41" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="109" t="s">
         <v>96</v>
       </c>
@@ -11563,7 +11885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="17.25" customHeight="1">
+    <row r="42" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="109" t="s">
         <v>97</v>
       </c>
@@ -11579,7 +11901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="17.25" customHeight="1">
+    <row r="43" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="109" t="s">
         <v>98</v>
       </c>
@@ -11595,7 +11917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="17.25" customHeight="1">
+    <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="109" t="s">
         <v>99</v>
       </c>
@@ -11611,7 +11933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="17.25" customHeight="1">
+    <row r="45" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="109" t="s">
         <v>100</v>
       </c>
@@ -11627,7 +11949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="17.25" customHeight="1">
+    <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="109" t="s">
         <v>101</v>
       </c>
@@ -11643,7 +11965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="17.25" customHeight="1">
+    <row r="47" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="109" t="s">
         <v>102</v>
       </c>
@@ -11659,7 +11981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="17.25" customHeight="1">
+    <row r="48" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="109" t="s">
         <v>103</v>
       </c>
@@ -11675,7 +11997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="17.25" customHeight="1">
+    <row r="49" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="109" t="s">
         <v>104</v>
       </c>
@@ -11691,7 +12013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="17.25" customHeight="1">
+    <row r="50" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="109" t="s">
         <v>105</v>
       </c>
@@ -11708,7 +12030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="17.25" customHeight="1">
+    <row r="51" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="109" t="s">
         <v>106</v>
       </c>
@@ -11725,7 +12047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="17.25" customHeight="1">
+    <row r="52" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="109" t="s">
         <v>107</v>
       </c>
@@ -11741,7 +12063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="17.25" customHeight="1">
+    <row r="53" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="109" t="s">
         <v>108</v>
       </c>
@@ -11757,7 +12079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="17.25" customHeight="1">
+    <row r="54" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="109" t="s">
         <v>109</v>
       </c>
@@ -11773,7 +12095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="17.25" customHeight="1">
+    <row r="55" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="109" t="s">
         <v>110</v>
       </c>
@@ -11789,7 +12111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="17.25" customHeight="1">
+    <row r="56" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="109" t="s">
         <v>111</v>
       </c>
@@ -11805,7 +12127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="17.25" customHeight="1">
+    <row r="57" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="109" t="s">
         <v>112</v>
       </c>
@@ -11821,7 +12143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="109" t="s">
         <v>113</v>
       </c>
@@ -11837,7 +12159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="17.25" customHeight="1">
+    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="109" t="s">
         <v>114</v>
       </c>
@@ -11853,7 +12175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="17.25" customHeight="1">
+    <row r="60" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="109" t="s">
         <v>115</v>
       </c>
@@ -11869,7 +12191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="17.25" customHeight="1">
+    <row r="61" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="109" t="s">
         <v>116</v>
       </c>
@@ -11885,7 +12207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="17.25" customHeight="1">
+    <row r="62" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="109" t="s">
         <v>117</v>
       </c>
@@ -11901,7 +12223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="17.25" customHeight="1">
+    <row r="63" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="109" t="s">
         <v>118</v>
       </c>
@@ -11917,7 +12239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="17.25" customHeight="1">
+    <row r="64" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="109" t="s">
         <v>119</v>
       </c>
@@ -11933,7 +12255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="17.25" customHeight="1">
+    <row r="65" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="109" t="s">
         <v>120</v>
       </c>
@@ -11949,7 +12271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="17.25" customHeight="1">
+    <row r="66" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="109" t="s">
         <v>121</v>
       </c>
@@ -11965,7 +12287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="17.25" customHeight="1">
+    <row r="67" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="109" t="s">
         <v>122</v>
       </c>
@@ -11981,7 +12303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="17.25" customHeight="1">
+    <row r="68" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="109" t="s">
         <v>123</v>
       </c>
@@ -11997,7 +12319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="17.25" customHeight="1">
+    <row r="69" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="109" t="s">
         <v>125</v>
       </c>
@@ -12013,7 +12335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="17.25" customHeight="1">
+    <row r="70" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="109" t="s">
         <v>127</v>
       </c>
@@ -12029,7 +12351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="17.25" customHeight="1">
+    <row r="71" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="109" t="s">
         <v>129</v>
       </c>
@@ -12045,7 +12367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="17.25" customHeight="1">
+    <row r="72" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="109" t="s">
         <v>130</v>
       </c>
@@ -12061,7 +12383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="17.25" customHeight="1">
+    <row r="73" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="109" t="s">
         <v>131</v>
       </c>
@@ -12077,7 +12399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="17.25" customHeight="1">
+    <row r="74" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="109" t="s">
         <v>132</v>
       </c>
@@ -12093,7 +12415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="17.25" customHeight="1">
+    <row r="75" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="109" t="s">
         <v>133</v>
       </c>
@@ -12109,7 +12431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="17.25" customHeight="1">
+    <row r="76" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="109" t="s">
         <v>134</v>
       </c>
@@ -12125,7 +12447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="17.25" customHeight="1">
+    <row r="77" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="109" t="s">
         <v>135</v>
       </c>
@@ -12141,7 +12463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="17.25" customHeight="1">
+    <row r="78" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="109" t="s">
         <v>136</v>
       </c>
@@ -12157,7 +12479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="17.25" customHeight="1">
+    <row r="79" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="109" t="s">
         <v>137</v>
       </c>
@@ -12173,7 +12495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="17.25" customHeight="1">
+    <row r="80" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="109" t="s">
         <v>138</v>
       </c>
@@ -12189,7 +12511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="17.25" customHeight="1">
+    <row r="81" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="109" t="s">
         <v>139</v>
       </c>
@@ -12205,7 +12527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="17.25" customHeight="1">
+    <row r="82" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="109" t="s">
         <v>141</v>
       </c>
@@ -12221,7 +12543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="17.25" customHeight="1">
+    <row r="83" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="109" t="s">
         <v>142</v>
       </c>
@@ -12237,7 +12559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="17.25" customHeight="1">
+    <row r="84" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="109" t="s">
         <v>143</v>
       </c>
@@ -12253,7 +12575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="17.25" customHeight="1">
+    <row r="85" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="109" t="s">
         <v>144</v>
       </c>
@@ -12269,7 +12591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="17.25" customHeight="1">
+    <row r="86" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="109" t="s">
         <v>146</v>
       </c>
@@ -12285,7 +12607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="17.25" customHeight="1">
+    <row r="87" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="109" t="s">
         <v>147</v>
       </c>
@@ -12301,7 +12623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="17.25" customHeight="1">
+    <row r="88" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="109" t="s">
         <v>148</v>
       </c>
@@ -12317,7 +12639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="17.25" customHeight="1">
+    <row r="89" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="109" t="s">
         <v>149</v>
       </c>
@@ -12333,7 +12655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="17.25" customHeight="1">
+    <row r="90" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="109" t="s">
         <v>150</v>
       </c>
@@ -12349,7 +12671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="17.25" customHeight="1">
+    <row r="91" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="109" t="s">
         <v>151</v>
       </c>
@@ -12365,7 +12687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="17.25" customHeight="1">
+    <row r="92" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="109" t="s">
         <v>152</v>
       </c>
@@ -12381,7 +12703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="17.25" customHeight="1">
+    <row r="93" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="109" t="s">
         <v>153</v>
       </c>
@@ -12397,7 +12719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="17.25" customHeight="1">
+    <row r="94" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="109" t="s">
         <v>154</v>
       </c>
@@ -12413,7 +12735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="17.25" customHeight="1">
+    <row r="95" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="109" t="s">
         <v>155</v>
       </c>
@@ -12429,7 +12751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="17.25" customHeight="1">
+    <row r="96" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="109" t="s">
         <v>156</v>
       </c>
@@ -12445,7 +12767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="17.25" customHeight="1">
+    <row r="97" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="109" t="s">
         <v>157</v>
       </c>
@@ -12461,7 +12783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="17.25" customHeight="1">
+    <row r="98" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="109" t="s">
         <v>158</v>
       </c>
@@ -12477,7 +12799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="17.25" customHeight="1">
+    <row r="99" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="109" t="s">
         <v>159</v>
       </c>
@@ -12493,21 +12815,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="17.25" customHeight="1">
+    <row r="100" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="109" t="s">
         <v>160</v>
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>46163.643839930555</v>
-      </c>
-      <c r="C100" s="110"/>
+        <v>46323.358679166668</v>
+      </c>
       <c r="D100" s="109">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="17.25" customHeight="1">
+    <row r="101" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="109" t="s">
         <v>161</v>
       </c>
@@ -12523,7 +12844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="17.25" customHeight="1">
+    <row r="102" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="109" t="s">
         <v>162</v>
       </c>
@@ -12539,7 +12860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="17.25" customHeight="1">
+    <row r="103" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="109" t="s">
         <v>163</v>
       </c>
@@ -12555,7 +12876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="17.25" customHeight="1">
+    <row r="104" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="109" t="s">
         <v>164</v>
       </c>
@@ -12571,7 +12892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="17.25" customHeight="1">
+    <row r="105" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="109" t="s">
         <v>165</v>
       </c>
@@ -12587,7 +12908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="17.25" customHeight="1">
+    <row r="106" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="109" t="s">
         <v>166</v>
       </c>
@@ -12603,7 +12924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="17.25" customHeight="1">
+    <row r="107" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="109" t="s">
         <v>167</v>
       </c>
@@ -12619,7 +12940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="17.25" customHeight="1">
+    <row r="108" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="109" t="s">
         <v>168</v>
       </c>
@@ -12635,7 +12956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="17.25" customHeight="1">
+    <row r="109" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="109" t="s">
         <v>169</v>
       </c>
@@ -12651,7 +12972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="17.25" customHeight="1">
+    <row r="110" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="109" t="s">
         <v>170</v>
       </c>
@@ -12667,7 +12988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="17.25" customHeight="1">
+    <row r="111" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="109" t="s">
         <v>171</v>
       </c>
@@ -12683,13 +13004,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="17.25" customHeight="1">
+    <row r="112" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="109"/>
       <c r="B112" s="109"/>
-      <c r="C112" s="110"/>
       <c r="D112" s="109"/>
     </row>
-    <row r="113" spans="1:4" ht="17.25" customHeight="1">
+    <row r="113" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="109" t="s">
         <v>172</v>
       </c>
@@ -12705,7 +13025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="17.25" customHeight="1">
+    <row r="114" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="109" t="s">
         <v>173</v>
       </c>
@@ -12721,7 +13041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="17.25" customHeight="1">
+    <row r="115" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="109" t="s">
         <v>175</v>
       </c>
@@ -12737,7 +13057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="17.25" customHeight="1">
+    <row r="116" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="109" t="s">
         <v>177</v>
       </c>
@@ -12753,7 +13073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="17.25" customHeight="1">
+    <row r="117" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="109" t="s">
         <v>178</v>
       </c>
@@ -12769,7 +13089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="17.25" customHeight="1">
+    <row r="118" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="109" t="s">
         <v>179</v>
       </c>
@@ -12785,7 +13105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="17.25" customHeight="1">
+    <row r="119" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="109" t="s">
         <v>180</v>
       </c>
@@ -12801,7 +13121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="17.25" customHeight="1">
+    <row r="120" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="109" t="s">
         <v>181</v>
       </c>
@@ -12817,7 +13137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="17.25" customHeight="1">
+    <row r="121" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="109" t="s">
         <v>182</v>
       </c>
@@ -12833,7 +13153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="17.25" customHeight="1">
+    <row r="122" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="109" t="s">
         <v>183</v>
       </c>
@@ -12849,7 +13169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="17.25" customHeight="1">
+    <row r="123" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="109" t="s">
         <v>184</v>
       </c>
@@ -12865,7 +13185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="17.25" customHeight="1">
+    <row r="124" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="109" t="s">
         <v>185</v>
       </c>
@@ -12881,7 +13201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="17.25" customHeight="1">
+    <row r="125" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="109" t="s">
         <v>186</v>
       </c>
@@ -12897,7 +13217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="17.25" customHeight="1">
+    <row r="126" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="109" t="s">
         <v>187</v>
       </c>
@@ -12913,7 +13233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="17.25" customHeight="1">
+    <row r="127" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="109" t="s">
         <v>188</v>
       </c>
@@ -12929,7 +13249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="17.25" customHeight="1">
+    <row r="128" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="109" t="s">
         <v>189</v>
       </c>
@@ -12945,7 +13265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="17.25" customHeight="1">
+    <row r="129" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="109" t="s">
         <v>190</v>
       </c>
@@ -12961,7 +13281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="17.25" customHeight="1">
+    <row r="130" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="109" t="s">
         <v>191</v>
       </c>
@@ -12977,7 +13297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="17.25" customHeight="1">
+    <row r="131" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="109" t="s">
         <v>192</v>
       </c>
@@ -12993,7 +13313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="17.25" customHeight="1">
+    <row r="132" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="109" t="s">
         <v>193</v>
       </c>
@@ -13009,7 +13329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="17.25" customHeight="1">
+    <row r="133" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="109" t="s">
         <v>194</v>
       </c>
@@ -13025,7 +13345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="17.25" customHeight="1">
+    <row r="134" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="109" t="s">
         <v>195</v>
       </c>
@@ -13041,7 +13361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="17.25" customHeight="1">
+    <row r="135" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="109" t="s">
         <v>196</v>
       </c>
@@ -13057,7 +13377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="17.25" customHeight="1">
+    <row r="136" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="109" t="s">
         <v>198</v>
       </c>
@@ -13073,7 +13393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="17.25" customHeight="1">
+    <row r="137" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="109" t="s">
         <v>199</v>
       </c>
@@ -13089,7 +13409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="17.25" customHeight="1">
+    <row r="138" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="109" t="s">
         <v>200</v>
       </c>
@@ -13105,7 +13425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="17.25" customHeight="1">
+    <row r="139" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="109" t="s">
         <v>201</v>
       </c>
@@ -13121,7 +13441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="17.25" customHeight="1">
+    <row r="140" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="109" t="s">
         <v>202</v>
       </c>
@@ -13137,7 +13457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="17.25" customHeight="1">
+    <row r="141" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="109" t="s">
         <v>203</v>
       </c>
@@ -13153,7 +13473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="17.25" customHeight="1">
+    <row r="142" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="109" t="s">
         <v>205</v>
       </c>
@@ -13169,7 +13489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="17.25" customHeight="1">
+    <row r="143" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="109" t="s">
         <v>206</v>
       </c>
@@ -13185,21 +13505,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="17.25" customHeight="1">
+    <row r="144" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="109" t="s">
         <v>207</v>
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
-      </c>
-      <c r="C144" s="110"/>
+        <v>46323</v>
+      </c>
       <c r="D144" s="109">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="17.25" customHeight="1">
+    <row r="145" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="109" t="s">
         <v>208</v>
       </c>
@@ -13215,7 +13534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="17.25" customHeight="1">
+    <row r="146" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="109" t="s">
         <v>210</v>
       </c>
@@ -13231,7 +13550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="17.25" customHeight="1">
+    <row r="147" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="109" t="s">
         <v>211</v>
       </c>
@@ -13247,7 +13566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="17.25" customHeight="1">
+    <row r="148" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="109" t="s">
         <v>213</v>
       </c>
@@ -13263,7 +13582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="17.25" customHeight="1">
+    <row r="149" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="109" t="s">
         <v>214</v>
       </c>
@@ -13279,7 +13598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="17.25" customHeight="1">
+    <row r="150" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="109" t="s">
         <v>215</v>
       </c>
@@ -13295,7 +13614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="17.25" customHeight="1">
+    <row r="151" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="109" t="s">
         <v>216</v>
       </c>
@@ -13311,7 +13630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="17.25" customHeight="1">
+    <row r="152" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="109" t="s">
         <v>217</v>
       </c>
@@ -13327,7 +13646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="17.25" customHeight="1">
+    <row r="153" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="109" t="s">
         <v>218</v>
       </c>
@@ -13343,7 +13662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="17.25" customHeight="1">
+    <row r="154" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="109" t="s">
         <v>219</v>
       </c>
@@ -13360,7 +13679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="17.25" customHeight="1">
+    <row r="155" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="109" t="s">
         <v>220</v>
       </c>
@@ -13376,7 +13695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="17.25" customHeight="1">
+    <row r="156" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="109" t="s">
         <v>221</v>
       </c>
@@ -13392,7 +13711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="17.25" customHeight="1">
+    <row r="157" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="109" t="s">
         <v>222</v>
       </c>
@@ -13408,7 +13727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="17.25" customHeight="1">
+    <row r="158" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="109" t="s">
         <v>223</v>
       </c>
@@ -13424,7 +13743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="17.25" customHeight="1">
+    <row r="159" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="109" t="s">
         <v>224</v>
       </c>
@@ -13440,7 +13759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="17.25" customHeight="1">
+    <row r="160" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="109" t="s">
         <v>225</v>
       </c>
@@ -13456,7 +13775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="17.25" customHeight="1">
+    <row r="161" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="109" t="s">
         <v>226</v>
       </c>
@@ -13472,7 +13791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="17.25" customHeight="1">
+    <row r="162" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="109" t="s">
         <v>227</v>
       </c>
@@ -13488,7 +13807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="17.25" customHeight="1">
+    <row r="163" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="109" t="s">
         <v>229</v>
       </c>
@@ -13506,10 +13825,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D180">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13524,7 +13843,7 @@
     <outlinePr summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R31"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="14.140625" customWidth="1"/>
@@ -13534,180 +13853,81 @@
     <col min="15" max="18" width="9.140625" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="110" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>230</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110" t="s">
+      <c r="C1" t="s">
         <v>231</v>
       </c>
       <c r="D1" s="115" t="s">
         <v>232</v>
       </c>
       <c r="E1" s="115"/>
-      <c r="F1" s="110" t="s">
+      <c r="F1" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="110"/>
       <c r="H1" s="34" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="110">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2">
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
       <c r="D2" s="115"/>
       <c r="E2" s="115"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110" t="str">
+      <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="110"/>
-      <c r="B3" s="110"/>
-      <c r="C3" s="110"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D3" s="85" t="s">
         <v>235</v>
       </c>
-      <c r="E3" s="110"/>
       <c r="F3" s="85" t="s">
         <v>236</v>
       </c>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
-    </row>
-    <row r="4" spans="1:8" hidden="1">
-      <c r="A4" s="110" t="s">
+    </row>
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>237</v>
       </c>
-      <c r="B4" s="110"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-    </row>
-    <row r="5" spans="1:8" ht="75" customHeight="1">
-      <c r="A5" s="110" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>238</v>
       </c>
-      <c r="B5" s="110"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-    </row>
-    <row r="10" spans="1:8" outlineLevel="1">
-      <c r="A10" s="110"/>
-      <c r="B10" s="110"/>
-      <c r="C10" s="110"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-    </row>
-    <row r="11" spans="1:8" outlineLevel="1">
-      <c r="A11" s="110"/>
-      <c r="B11" s="110"/>
-      <c r="C11" s="110"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-    </row>
-    <row r="12" spans="1:8" hidden="1" outlineLevel="2">
-      <c r="A12" s="110"/>
-      <c r="B12" s="110"/>
-      <c r="C12" s="110"/>
-      <c r="D12" s="110"/>
-      <c r="E12" s="110"/>
-      <c r="F12" s="110"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
-    </row>
-    <row r="13" spans="1:8" hidden="1" outlineLevel="2">
-      <c r="A13" s="110"/>
-      <c r="B13" s="110"/>
-      <c r="C13" s="110"/>
-      <c r="D13" s="110"/>
-      <c r="E13" s="110"/>
-      <c r="F13" s="110"/>
-      <c r="G13" s="110"/>
-      <c r="H13" s="110"/>
-    </row>
-    <row r="14" spans="1:8" hidden="1" outlineLevel="2">
-      <c r="A14" s="110"/>
-      <c r="B14" s="110"/>
-      <c r="C14" s="110"/>
-      <c r="D14" s="110"/>
-      <c r="E14" s="110"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-    </row>
-    <row r="15" spans="1:8" outlineLevel="1" collapsed="1">
-      <c r="A15" s="110"/>
-      <c r="B15" s="110"/>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
-    </row>
-    <row r="16" spans="1:8" outlineLevel="1">
-      <c r="A16" s="110"/>
-      <c r="B16" s="110"/>
-      <c r="C16" s="110"/>
-      <c r="D16" s="110"/>
-      <c r="E16" s="110"/>
-      <c r="F16" s="110"/>
-      <c r="G16" s="110"/>
-      <c r="H16" s="110"/>
-    </row>
-    <row r="17" spans="1:2" outlineLevel="1">
-      <c r="A17" s="110"/>
-      <c r="B17" s="110"/>
-    </row>
-    <row r="18" spans="1:2" outlineLevel="1">
-      <c r="A18" s="110"/>
-      <c r="B18" s="110"/>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="110" cm="1">
+    </row>
+    <row r="10" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:8" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="1:2" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:2" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" cm="1">
         <f t="array" aca="1" ref="A30:B31" ca="1">_xlfn.RANDARRAY(2,2)</f>
-        <v>0.16856857803156</v>
-      </c>
-      <c r="B30" s="110">
+        <v>0.18616970653222542</v>
+      </c>
+      <c r="B30">
         <f ca="1"/>
-        <v>0.3860749301684725</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="110">
+        <v>0.22504048945622568</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
         <f ca="1"/>
-        <v>1.8573067417372524E-2</v>
-      </c>
-      <c r="B31" s="110">
+        <v>0.13755110210467758</v>
+      </c>
+      <c r="B31">
         <f ca="1"/>
-        <v>0.13795799514875995</v>
+        <v>0.6918699284640335</v>
       </c>
     </row>
   </sheetData>
@@ -13726,64 +13946,54 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF68F2C0-1053-4FB6-BD74-8A11B0CAF123}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17.85546875" customWidth="1"/>
     <col min="5" max="5" width="18.140625" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="13.5" thickBot="1">
+    <row r="1" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="68" t="s">
         <v>239</v>
       </c>
-      <c r="B1" s="110"/>
       <c r="C1" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="D1" s="110"/>
       <c r="E1" s="35" t="s">
         <v>241</v>
       </c>
       <c r="F1" s="36"/>
-      <c r="G1" s="110"/>
       <c r="H1" s="34" t="s">
         <v>242</v>
       </c>
-      <c r="I1" s="110"/>
       <c r="J1" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="K1" s="110"/>
       <c r="L1" s="93" t="s">
         <v>244</v>
       </c>
       <c r="M1" s="36"/>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="B2" s="110"/>
       <c r="C2" s="86" t="s">
         <v>246</v>
       </c>
-      <c r="D2" s="110"/>
       <c r="E2" s="38" t="s">
         <v>247</v>
       </c>
       <c r="F2" s="21" t="s">
         <v>248</v>
       </c>
-      <c r="G2" s="110"/>
       <c r="H2" s="72" t="s">
         <v>249</v>
       </c>
-      <c r="I2" s="110"/>
       <c r="J2" s="83" t="s">
         <v>250</v>
       </c>
-      <c r="K2" s="110"/>
       <c r="L2" s="21" t="s">
         <v>251</v>
       </c>
@@ -13791,28 +14001,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="41" t="s">
         <v>252</v>
       </c>
-      <c r="B3" s="110"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
       <c r="E3" s="38" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="G3" s="110"/>
       <c r="H3" s="71" t="s">
         <v>253</v>
       </c>
-      <c r="I3" s="110"/>
       <c r="J3" s="73" t="s">
         <v>254</v>
       </c>
-      <c r="K3" s="110"/>
       <c r="L3" s="21" t="s">
         <v>255</v>
       </c>
@@ -13820,30 +14024,25 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15">
+    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="42" t="s">
         <v>256</v>
       </c>
-      <c r="B4" s="110"/>
       <c r="C4" s="56" t="s">
         <v>257</v>
       </c>
-      <c r="D4" s="110"/>
       <c r="E4" s="38" t="s">
         <v>258</v>
       </c>
       <c r="F4" s="24" t="s">
         <v>248</v>
       </c>
-      <c r="G4" s="110"/>
       <c r="H4" s="34" t="s">
         <v>259</v>
       </c>
-      <c r="I4" s="110"/>
       <c r="J4" s="84" t="s">
         <v>260</v>
       </c>
-      <c r="K4" s="110"/>
       <c r="L4" s="21" t="s">
         <v>261</v>
       </c>
@@ -13851,26 +14050,19 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
         <v>262</v>
       </c>
-      <c r="B5" s="110"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
       <c r="E5" s="38" t="s">
         <v>263</v>
       </c>
       <c r="F5" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="G5" s="110"/>
       <c r="H5" s="70" t="s">
         <v>264</v>
       </c>
-      <c r="I5" s="110"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="110"/>
       <c r="L5" s="21" t="s">
         <v>265</v>
       </c>
@@ -13878,28 +14070,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="B6" s="110"/>
       <c r="C6" s="57" t="s">
         <v>267</v>
       </c>
-      <c r="D6" s="110"/>
       <c r="E6" s="38" t="s">
         <v>268</v>
       </c>
       <c r="F6" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="G6" s="110"/>
       <c r="H6" s="69" t="s">
         <v>269</v>
       </c>
-      <c r="I6" s="110"/>
-      <c r="J6" s="110"/>
-      <c r="K6" s="110"/>
       <c r="L6" s="21" t="s">
         <v>270</v>
       </c>
@@ -13907,26 +14093,19 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75">
+    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="45" t="s">
         <v>271</v>
       </c>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
       <c r="E7" s="38" t="s">
         <v>272</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="G7" s="110"/>
       <c r="H7" s="82" t="s">
         <v>273</v>
       </c>
-      <c r="I7" s="110"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="110"/>
       <c r="L7" s="38" t="s">
         <v>274</v>
       </c>
@@ -13934,28 +14113,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21">
+    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.35">
       <c r="A8" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="B8" s="110"/>
       <c r="C8" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="D8" s="110"/>
       <c r="E8" s="38" t="s">
         <v>277</v>
       </c>
       <c r="F8" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="G8" s="110"/>
       <c r="H8" s="81" t="s">
         <v>278</v>
       </c>
-      <c r="I8" s="110"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="110"/>
       <c r="L8" s="38" t="s">
         <v>279</v>
       </c>
@@ -13963,24 +14136,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="B9" s="110"/>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110"/>
       <c r="E9" s="38" t="s">
         <v>281</v>
       </c>
       <c r="F9" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="110"/>
-      <c r="K9" s="110"/>
       <c r="L9" s="38" t="s">
         <v>282</v>
       </c>
@@ -13988,202 +14153,122 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="B10" s="110"/>
       <c r="C10" s="59" t="s">
         <v>284</v>
       </c>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="110"/>
-      <c r="M10" s="110"/>
-    </row>
-    <row r="11" spans="1:13" ht="13.5" thickBot="1">
+    </row>
+    <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="49" t="s">
         <v>285</v>
       </c>
-      <c r="B11" s="110"/>
-      <c r="C11" s="110"/>
-      <c r="D11" s="110"/>
       <c r="E11" s="35" t="s">
         <v>286</v>
       </c>
       <c r="F11" s="36"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="110"/>
-      <c r="K11" s="110"/>
-      <c r="L11" s="110"/>
-      <c r="M11" s="110"/>
-    </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1">
+    </row>
+    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="50" t="s">
         <v>287</v>
       </c>
-      <c r="B12" s="110"/>
       <c r="C12" s="60" t="s">
         <v>288</v>
       </c>
-      <c r="D12" s="110"/>
       <c r="E12" s="38" t="s">
         <v>289</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>248</v>
       </c>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="110"/>
-      <c r="K12" s="110"/>
-      <c r="L12" s="110"/>
-      <c r="M12" s="110"/>
-    </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+    </row>
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="51" t="s">
         <v>290</v>
       </c>
-      <c r="B13" s="110"/>
-      <c r="C13" s="110"/>
-      <c r="D13" s="110"/>
       <c r="E13" s="38" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="G13" s="110"/>
-      <c r="H13" s="110"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="110"/>
-      <c r="K13" s="110"/>
-      <c r="L13" s="110"/>
-      <c r="M13" s="110"/>
-    </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+    </row>
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="52" t="s">
         <v>291</v>
       </c>
-      <c r="B14" s="110"/>
       <c r="C14" s="61" t="s">
         <v>292</v>
       </c>
-      <c r="D14" s="110"/>
       <c r="E14" s="38" t="s">
         <v>258</v>
       </c>
       <c r="F14" s="31" t="s">
         <v>248</v>
       </c>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="110"/>
-      <c r="L14" s="110"/>
-      <c r="M14" s="110"/>
-    </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+    </row>
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="53" t="s">
         <v>293</v>
       </c>
-      <c r="B15" s="110"/>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
       <c r="E15" s="38" t="s">
         <v>272</v>
       </c>
       <c r="F15" s="32" t="s">
         <v>248</v>
       </c>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
-      <c r="I15" s="110"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="110"/>
-      <c r="M15" s="110"/>
-    </row>
-    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
+    </row>
+    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="54" t="s">
         <v>294</v>
       </c>
-      <c r="B16" s="110"/>
       <c r="C16" s="62" t="s">
         <v>295</v>
       </c>
-      <c r="D16" s="110"/>
       <c r="E16" s="38" t="s">
         <v>281</v>
       </c>
       <c r="F16" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="G16" s="110"/>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110"/>
-      <c r="J16" s="110"/>
-      <c r="K16" s="110"/>
-      <c r="L16" s="110"/>
-      <c r="M16" s="110"/>
-    </row>
-    <row r="17" spans="1:6" ht="13.5" thickBot="1">
+    </row>
+    <row r="17" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="55" t="s">
         <v>296</v>
       </c>
-      <c r="B17" s="110"/>
-      <c r="C17" s="110"/>
-      <c r="D17" s="110"/>
-      <c r="E17" s="110"/>
-      <c r="F17" s="110"/>
-    </row>
-    <row r="18" spans="1:6" ht="13.5" thickBot="1">
+    </row>
+    <row r="18" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="74" t="s">
         <v>297</v>
       </c>
-      <c r="B18" s="110"/>
       <c r="C18" s="63" t="s">
         <v>298</v>
       </c>
-      <c r="D18" s="110"/>
       <c r="E18" s="35" t="s">
         <v>299</v>
       </c>
       <c r="F18" s="36"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" thickBot="1">
+    <row r="19" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="75" t="s">
         <v>300</v>
       </c>
-      <c r="B19" s="110"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="110"/>
       <c r="E19" s="38" t="s">
         <v>301</v>
       </c>
-      <c r="F19" s="110" t="s">
+      <c r="F19" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="51.75" thickBot="1">
+    <row r="20" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="76" t="s">
         <v>303</v>
       </c>
-      <c r="B20" s="110"/>
       <c r="C20" s="64" t="s">
         <v>304</v>
       </c>
-      <c r="D20" s="110"/>
       <c r="E20" s="38" t="s">
         <v>305</v>
       </c>
@@ -14191,103 +14276,52 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="13.5" thickBot="1">
+    <row r="21" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="77" t="s">
         <v>306</v>
       </c>
-      <c r="B21" s="110"/>
-      <c r="C21" s="110"/>
-      <c r="D21" s="110"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="110"/>
-    </row>
-    <row r="22" spans="1:6" ht="13.5" thickBot="1">
+    </row>
+    <row r="22" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="78" t="s">
         <v>307</v>
       </c>
-      <c r="B22" s="110"/>
       <c r="C22" s="65" t="s">
         <v>308</v>
       </c>
-      <c r="D22" s="110"/>
       <c r="E22" s="21"/>
-      <c r="F22" s="110"/>
-    </row>
-    <row r="23" spans="1:6" ht="13.5" thickBot="1">
+    </row>
+    <row r="23" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="79" t="s">
         <v>309</v>
       </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="110"/>
-      <c r="D23" s="110"/>
       <c r="E23" s="21"/>
-      <c r="F23" s="110"/>
-    </row>
-    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
+    </row>
+    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="80" t="s">
         <v>310</v>
       </c>
-      <c r="B24" s="110"/>
       <c r="C24" s="66" t="s">
         <v>311</v>
       </c>
-      <c r="D24" s="110"/>
       <c r="E24" s="21"/>
-      <c r="F24" s="110"/>
-    </row>
-    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
-      <c r="A25" s="110"/>
-      <c r="B25" s="110"/>
-      <c r="C25" s="110"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="110"/>
-    </row>
-    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
-      <c r="A26" s="110"/>
-      <c r="B26" s="110"/>
+    </row>
+    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C26" s="67" t="s">
         <v>312</v>
       </c>
-      <c r="D26" s="110"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="110"/>
-    </row>
-    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
-      <c r="A27" s="110"/>
-      <c r="B27" s="110"/>
-      <c r="C27" s="110"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="110"/>
-    </row>
-    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
-      <c r="A28" s="110"/>
-      <c r="B28" s="110"/>
+    </row>
+    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C28" s="88" t="s">
         <v>313</v>
       </c>
-      <c r="D28" s="110"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="110"/>
-    </row>
-    <row r="29" spans="1:6" ht="13.5" thickTop="1">
-      <c r="A29" s="110"/>
-      <c r="B29" s="110"/>
-      <c r="C29" s="110"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="110"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="110"/>
-      <c r="B30" s="110"/>
+    </row>
+    <row r="29" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C30" s="87" t="s">
         <v>314</v>
       </c>
-      <c r="D30" s="110"/>
-      <c r="E30" s="110"/>
-      <c r="F30" s="110"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14298,13 +14332,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919E811-4385-4D35-A19E-3B7E0E659A89}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.5" thickBot="1">
+    <row r="1" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
         <v>315</v>
       </c>
@@ -14314,9 +14348,6 @@
       <c r="C1" s="35" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
       <c r="G1" s="35" t="s">
         <v>318</v>
       </c>
@@ -14324,33 +14355,30 @@
       <c r="I1" s="36"/>
       <c r="J1" s="36"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="38" t="s">
         <v>319</v>
       </c>
-      <c r="B2" s="110">
+      <c r="B2">
         <v>3</v>
       </c>
-      <c r="C2" s="110">
-        <v>1</v>
-      </c>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="G2" s="34" t="s">
         <v>320</v>
       </c>
       <c r="H2" s="21">
         <v>5</v>
       </c>
-      <c r="I2" s="110">
+      <c r="I2">
         <v>3</v>
       </c>
       <c r="J2" s="21">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="38" t="s">
         <v>321</v>
       </c>
@@ -14360,74 +14388,64 @@
       <c r="C3" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
       <c r="G3" s="34" t="s">
         <v>324</v>
       </c>
-      <c r="H3" s="110">
+      <c r="H3">
         <v>5</v>
       </c>
-      <c r="I3" s="110">
+      <c r="I3">
         <v>3</v>
       </c>
-      <c r="J3" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="38" t="s">
         <v>325</v>
       </c>
-      <c r="B4" s="110"/>
       <c r="C4" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
       <c r="G4" s="34" t="s">
         <v>327</v>
       </c>
-      <c r="H4" s="110">
+      <c r="H4">
         <v>5</v>
       </c>
-      <c r="I4" s="110">
+      <c r="I4">
         <v>3</v>
       </c>
-      <c r="J4" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
         <v>328</v>
       </c>
-      <c r="B5" s="110" t="e">
+      <c r="B5" t="e">
         <f>0/0</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C5" s="110">
+      <c r="C5">
         <v>0</v>
       </c>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
       <c r="G5" s="34" t="s">
         <v>329</v>
       </c>
-      <c r="H5" s="110">
+      <c r="H5">
         <v>5</v>
       </c>
-      <c r="I5" s="110">
+      <c r="I5">
         <v>3</v>
       </c>
-      <c r="J5" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
         <v>330</v>
       </c>
@@ -14437,23 +14455,20 @@
       <c r="C6" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
       <c r="G6" s="34" t="s">
         <v>332</v>
       </c>
-      <c r="H6" s="110">
+      <c r="H6">
         <v>5</v>
       </c>
-      <c r="I6" s="110">
+      <c r="I6">
         <v>3</v>
       </c>
-      <c r="J6" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="J6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="38" t="s">
         <v>333</v>
       </c>
@@ -14466,22 +14481,20 @@
       <c r="D7" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="E7" s="110"/>
-      <c r="F7" s="110"/>
       <c r="G7" s="34" t="s">
         <v>336</v>
       </c>
-      <c r="H7" s="110">
+      <c r="H7">
         <v>5</v>
       </c>
-      <c r="I7" s="110">
+      <c r="I7">
         <v>3</v>
       </c>
-      <c r="J7" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
         <v>337</v>
       </c>
@@ -14491,15 +14504,8 @@
       <c r="C8" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="110"/>
-    </row>
-    <row r="9" spans="1:10">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="38" t="s">
         <v>339</v>
       </c>
@@ -14507,28 +14513,18 @@
         <v>326</v>
       </c>
       <c r="C9" s="21"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="110"/>
-    </row>
-    <row r="10" spans="1:10" ht="13.5" thickBot="1">
+    </row>
+    <row r="10" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="38" t="s">
         <v>340</v>
       </c>
-      <c r="B10" s="110">
+      <c r="B10">
         <v>0</v>
       </c>
-      <c r="C10" s="110" t="e">
+      <c r="C10" t="e">
         <f>0/0</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
       <c r="G10" s="35" t="s">
         <v>341</v>
       </c>
@@ -14536,7 +14532,7 @@
       <c r="I10" s="36"/>
       <c r="J10" s="36"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="38" t="s">
         <v>342</v>
       </c>
@@ -14546,77 +14542,68 @@
       <c r="C11" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
       <c r="G11" s="34" t="s">
         <v>343</v>
       </c>
-      <c r="H11" s="110">
+      <c r="H11">
         <v>5</v>
       </c>
-      <c r="I11" s="110">
+      <c r="I11">
         <v>3</v>
       </c>
-      <c r="J11" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="J11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="38" t="s">
         <v>344</v>
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46323</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
         <v>40453</v>
       </c>
-      <c r="D12" s="110"/>
-      <c r="E12" s="110"/>
-      <c r="F12" s="110"/>
       <c r="G12" s="34" t="s">
         <v>345</v>
       </c>
-      <c r="H12" s="110">
+      <c r="H12">
         <v>5</v>
       </c>
-      <c r="I12" s="110">
+      <c r="I12">
         <v>3</v>
       </c>
-      <c r="J12" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="J12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="B13" s="110">
+      <c r="B13">
         <v>7</v>
       </c>
-      <c r="C13" s="110">
+      <c r="C13">
         <v>5</v>
       </c>
-      <c r="D13" s="110"/>
-      <c r="E13" s="110"/>
-      <c r="F13" s="110"/>
       <c r="G13" s="34" t="s">
         <v>347</v>
       </c>
-      <c r="H13" s="110">
+      <c r="H13">
         <v>5</v>
       </c>
-      <c r="I13" s="110">
+      <c r="I13">
         <v>3</v>
       </c>
-      <c r="J13" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="J13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="38" t="s">
         <v>348</v>
       </c>
@@ -14629,474 +14616,391 @@
       <c r="D14" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="E14" s="110"/>
-      <c r="F14" s="110"/>
       <c r="G14" s="34" t="s">
         <v>349</v>
       </c>
-      <c r="H14" s="110">
+      <c r="H14">
         <v>5</v>
       </c>
-      <c r="I14" s="110">
+      <c r="I14">
         <v>3</v>
       </c>
-      <c r="J14" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="J14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="38" t="s">
         <v>350</v>
       </c>
-      <c r="B15" s="110">
-        <v>1</v>
-      </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="110"/>
+      <c r="B15">
+        <v>1</v>
+      </c>
       <c r="G15" s="34" t="s">
         <v>351</v>
       </c>
-      <c r="H15" s="110">
+      <c r="H15">
         <v>5</v>
       </c>
-      <c r="I15" s="110">
+      <c r="I15">
         <v>3</v>
       </c>
-      <c r="J15" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="J15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="38" t="s">
         <v>352</v>
       </c>
-      <c r="B16" s="110">
+      <c r="B16">
         <v>2</v>
       </c>
-      <c r="C16" s="110">
-        <v>1</v>
-      </c>
-      <c r="D16" s="110"/>
-      <c r="E16" s="110"/>
-      <c r="F16" s="110"/>
+      <c r="C16">
+        <v>1</v>
+      </c>
       <c r="G16" s="34" t="s">
         <v>353</v>
       </c>
-      <c r="H16" s="110">
+      <c r="H16">
         <v>5</v>
       </c>
-      <c r="I16" s="110">
+      <c r="I16">
         <v>3</v>
       </c>
-      <c r="J16" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="J16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="38" t="s">
         <v>354</v>
       </c>
-      <c r="B17" s="110">
+      <c r="B17">
         <v>0</v>
       </c>
-      <c r="C17" s="110">
+      <c r="C17">
         <v>2</v>
       </c>
-      <c r="D17" s="110"/>
-      <c r="E17" s="110"/>
-      <c r="F17" s="110"/>
       <c r="G17" s="34" t="s">
         <v>355</v>
       </c>
-      <c r="H17" s="110">
+      <c r="H17">
         <v>5</v>
       </c>
-      <c r="I17" s="110">
+      <c r="I17">
         <v>3</v>
       </c>
-      <c r="J17" s="110">
-        <v>1</v>
-      </c>
-      <c r="K17" s="110"/>
-      <c r="L17" s="110"/>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="J17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="38" t="s">
         <v>356</v>
       </c>
-      <c r="B18" s="110">
+      <c r="B18">
         <v>3</v>
       </c>
-      <c r="C18" s="110">
+      <c r="C18">
         <v>0</v>
       </c>
-      <c r="D18" s="110"/>
-      <c r="E18" s="110"/>
-      <c r="F18" s="110"/>
       <c r="G18" s="34" t="s">
         <v>357</v>
       </c>
-      <c r="H18" s="110">
+      <c r="H18">
         <v>5</v>
       </c>
-      <c r="I18" s="110">
+      <c r="I18">
         <v>3</v>
       </c>
-      <c r="J18" s="110">
-        <v>1</v>
-      </c>
-      <c r="K18" s="110"/>
-      <c r="L18" s="110"/>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="J18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="B19" s="110">
+      <c r="B19">
         <v>2</v>
       </c>
-      <c r="C19" s="110">
+      <c r="C19">
         <v>0</v>
       </c>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="110"/>
       <c r="G19" s="34" t="s">
         <v>359</v>
       </c>
-      <c r="H19" s="110">
+      <c r="H19">
         <v>5</v>
       </c>
-      <c r="I19" s="110">
+      <c r="I19">
         <v>3</v>
       </c>
-      <c r="J19" s="110">
-        <v>1</v>
-      </c>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="J19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="38" t="s">
         <v>360</v>
       </c>
-      <c r="B20" s="110">
+      <c r="B20">
         <v>0</v>
       </c>
-      <c r="C20" s="110">
+      <c r="C20">
         <v>2</v>
       </c>
-      <c r="D20" s="110"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="110"/>
       <c r="G20" s="34" t="s">
         <v>361</v>
       </c>
-      <c r="H20" s="110">
+      <c r="H20">
         <v>5</v>
       </c>
-      <c r="I20" s="110">
+      <c r="I20">
         <v>3</v>
       </c>
-      <c r="J20" s="110">
-        <v>1</v>
-      </c>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="J20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="38" t="s">
         <v>362</v>
       </c>
-      <c r="B21" s="110">
+      <c r="B21">
         <v>2</v>
       </c>
-      <c r="C21" s="110">
+      <c r="C21">
         <v>3</v>
       </c>
-      <c r="D21" s="110"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="110"/>
       <c r="G21" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="H21" s="110">
+      <c r="H21">
         <v>5</v>
       </c>
-      <c r="I21" s="110">
+      <c r="I21">
         <v>4</v>
       </c>
-      <c r="J21" s="110">
+      <c r="J21">
         <v>3</v>
       </c>
-      <c r="K21" s="110">
+      <c r="K21">
         <v>2</v>
       </c>
-      <c r="L21" s="110"/>
-    </row>
-    <row r="22" spans="1:12">
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="38" t="s">
         <v>364</v>
       </c>
-      <c r="B22" s="110">
+      <c r="B22">
         <v>2</v>
       </c>
-      <c r="C22" s="110">
+      <c r="C22">
         <v>0</v>
       </c>
-      <c r="D22" s="110"/>
-      <c r="E22" s="110"/>
-      <c r="F22" s="110"/>
       <c r="G22" s="34" t="s">
         <v>365</v>
       </c>
-      <c r="H22" s="110">
+      <c r="H22">
         <v>5</v>
       </c>
-      <c r="I22" s="110">
+      <c r="I22">
         <v>4</v>
       </c>
-      <c r="J22" s="110">
+      <c r="J22">
         <v>3</v>
       </c>
-      <c r="K22" s="110">
+      <c r="K22">
         <v>2</v>
       </c>
-      <c r="L22" s="110"/>
-    </row>
-    <row r="23" spans="1:12">
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="38" t="s">
         <v>366</v>
       </c>
-      <c r="B23" s="110">
-        <v>1</v>
-      </c>
-      <c r="C23" s="110">
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
         <v>2</v>
       </c>
-      <c r="D23" s="110"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="110"/>
       <c r="G23" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="H23" s="110">
+      <c r="H23">
         <v>5</v>
       </c>
-      <c r="I23" s="110">
+      <c r="I23">
         <v>4</v>
       </c>
-      <c r="J23" s="110">
+      <c r="J23">
         <v>3</v>
       </c>
-      <c r="K23" s="110">
+      <c r="K23">
         <v>2</v>
       </c>
-      <c r="L23" s="110"/>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="110"/>
-      <c r="B24" s="110"/>
-      <c r="C24" s="110"/>
-      <c r="D24" s="110"/>
-      <c r="E24" s="110"/>
-      <c r="F24" s="110"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G24" s="34" t="s">
         <v>368</v>
       </c>
-      <c r="H24" s="110">
+      <c r="H24">
         <v>5</v>
       </c>
-      <c r="I24" s="110">
+      <c r="I24">
         <v>4</v>
       </c>
-      <c r="J24" s="110">
+      <c r="J24">
         <v>3</v>
       </c>
-      <c r="K24" s="110">
+      <c r="K24">
         <v>2</v>
       </c>
-      <c r="L24" s="110"/>
-    </row>
-    <row r="25" spans="1:12">
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="38" t="s">
         <v>369</v>
       </c>
-      <c r="B25" s="110">
+      <c r="B25">
         <v>5</v>
       </c>
-      <c r="C25" s="110">
+      <c r="C25">
         <v>2</v>
       </c>
-      <c r="D25" s="110"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="110"/>
       <c r="G25" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="H25" s="110">
+      <c r="H25">
         <v>5</v>
       </c>
-      <c r="I25" s="110">
+      <c r="I25">
         <v>4</v>
       </c>
-      <c r="J25" s="110">
+      <c r="J25">
         <v>3</v>
       </c>
-      <c r="K25" s="110">
+      <c r="K25">
         <v>2</v>
       </c>
-      <c r="L25" s="110"/>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="110"/>
-      <c r="B26" s="110"/>
-      <c r="C26" s="110"/>
-      <c r="D26" s="110"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="110"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G26" s="34" t="s">
         <v>371</v>
       </c>
-      <c r="H26" s="110">
+      <c r="H26">
         <v>5</v>
       </c>
-      <c r="I26" s="110">
+      <c r="I26">
         <v>4</v>
       </c>
-      <c r="J26" s="110">
+      <c r="J26">
         <v>3</v>
       </c>
-      <c r="K26" s="110">
+      <c r="K26">
         <v>2</v>
       </c>
-      <c r="L26" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="L26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="21" t="s">
         <v>372</v>
       </c>
-      <c r="B27" s="110">
+      <c r="B27">
         <v>2</v>
       </c>
-      <c r="C27" s="110"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="110"/>
       <c r="G27" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="H27" s="110">
+      <c r="H27">
         <v>5</v>
       </c>
-      <c r="I27" s="110">
+      <c r="I27">
         <v>4</v>
       </c>
-      <c r="J27" s="110">
+      <c r="J27">
         <v>3</v>
       </c>
-      <c r="K27" s="110">
+      <c r="K27">
         <v>2</v>
       </c>
-      <c r="L27" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="110"/>
-      <c r="B28" s="110"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="110"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="110"/>
+      <c r="L27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G28" s="34" t="s">
         <v>374</v>
       </c>
-      <c r="H28" s="110">
+      <c r="H28">
         <v>5</v>
       </c>
-      <c r="I28" s="110">
+      <c r="I28">
         <v>4</v>
       </c>
-      <c r="J28" s="110">
+      <c r="J28">
         <v>3</v>
       </c>
-      <c r="K28" s="110">
+      <c r="K28">
         <v>2</v>
       </c>
-      <c r="L28" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="L28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="38" t="s">
         <v>375</v>
       </c>
-      <c r="B29" s="110">
+      <c r="B29">
         <v>3</v>
       </c>
-      <c r="C29" s="110">
+      <c r="C29">
         <v>10</v>
       </c>
-      <c r="D29" s="110"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="110"/>
       <c r="G29" s="34" t="s">
         <v>376</v>
       </c>
-      <c r="H29" s="110">
+      <c r="H29">
         <v>5</v>
       </c>
-      <c r="I29" s="110">
+      <c r="I29">
         <v>4</v>
       </c>
-      <c r="J29" s="110">
+      <c r="J29">
         <v>3</v>
       </c>
-      <c r="K29" s="110">
+      <c r="K29">
         <v>2</v>
       </c>
-      <c r="L29" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="110"/>
-      <c r="B30" s="110"/>
-      <c r="C30" s="110"/>
-      <c r="D30" s="110"/>
-      <c r="E30" s="110"/>
-      <c r="F30" s="110"/>
+      <c r="L29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G30" s="34" t="s">
         <v>377</v>
       </c>
-      <c r="H30" s="110">
+      <c r="H30">
         <v>5</v>
       </c>
-      <c r="I30" s="110">
+      <c r="I30">
         <v>4</v>
       </c>
-      <c r="J30" s="110">
+      <c r="J30">
         <v>3</v>
       </c>
-      <c r="K30" s="110">
+      <c r="K30">
         <v>2</v>
       </c>
-      <c r="L30" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="13.5" thickBot="1">
-      <c r="A31" s="110"/>
-      <c r="B31" s="110"/>
-      <c r="C31" s="110"/>
-      <c r="D31" s="110"/>
-      <c r="E31" s="110"/>
-      <c r="F31" s="110"/>
+      <c r="L30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G31" s="35" t="s">
         <v>378</v>
       </c>
@@ -15109,208 +15013,195 @@
       <c r="J31" s="36">
         <v>1</v>
       </c>
-      <c r="K31" s="110"/>
-      <c r="L31" s="110"/>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="110"/>
-      <c r="B32" s="110"/>
-      <c r="C32" s="110"/>
-      <c r="D32" s="110"/>
-      <c r="E32" s="110"/>
-      <c r="F32" s="110"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G32" s="34" t="s">
         <v>379</v>
       </c>
-      <c r="H32" s="110">
+      <c r="H32">
         <v>5</v>
       </c>
-      <c r="I32" s="110">
+      <c r="I32">
         <v>3</v>
       </c>
-      <c r="J32" s="110">
-        <v>1</v>
-      </c>
-      <c r="K32" s="110"/>
-      <c r="L32" s="110"/>
-    </row>
-    <row r="33" spans="7:10">
+      <c r="J32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G33" s="34" t="s">
         <v>380</v>
       </c>
-      <c r="H33" s="110">
+      <c r="H33">
         <v>5</v>
       </c>
-      <c r="I33" s="110">
+      <c r="I33">
         <v>3</v>
       </c>
-      <c r="J33" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="7:10">
+      <c r="J33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G34" s="34" t="s">
         <v>381</v>
       </c>
-      <c r="H34" s="110">
+      <c r="H34">
         <v>5</v>
       </c>
-      <c r="I34" s="110">
+      <c r="I34">
         <v>3</v>
       </c>
-      <c r="J34" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="7:10">
+      <c r="J34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G35" s="34" t="s">
         <v>382</v>
       </c>
-      <c r="H35" s="110">
+      <c r="H35">
         <v>5</v>
       </c>
-      <c r="I35" s="110">
+      <c r="I35">
         <v>3</v>
       </c>
-      <c r="J35" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="7:10">
+      <c r="J35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G36" s="34" t="s">
         <v>383</v>
       </c>
-      <c r="H36" s="110">
+      <c r="H36">
         <v>5</v>
       </c>
-      <c r="I36" s="110">
+      <c r="I36">
         <v>3</v>
       </c>
-      <c r="J36" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="7:10">
+      <c r="J36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G37" s="34" t="s">
         <v>384</v>
       </c>
-      <c r="H37" s="110">
+      <c r="H37">
         <v>5</v>
       </c>
-      <c r="I37" s="110">
+      <c r="I37">
         <v>3</v>
       </c>
-      <c r="J37" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="7:10">
+      <c r="J37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G39" s="34"/>
-      <c r="H39" s="110"/>
-      <c r="I39" s="110"/>
-      <c r="J39" s="110"/>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="B15">
-    <cfRule type="expression" dxfId="41" priority="59">
+    <cfRule type="expression" dxfId="23" priority="59">
       <formula>ODD(B15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="cellIs" dxfId="40" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="47" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2">
-    <cfRule type="aboveAverage" dxfId="39" priority="115"/>
+    <cfRule type="aboveAverage" dxfId="21" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="beginsWith" dxfId="38" priority="74" operator="beginsWith" text="rule">
+    <cfRule type="beginsWith" dxfId="20" priority="74" operator="beginsWith" text="rule">
       <formula>LEFT(B3,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="containsBlanks" dxfId="37" priority="72">
+    <cfRule type="containsBlanks" dxfId="19" priority="72">
       <formula>LEN(TRIM(B4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:C5">
-    <cfRule type="containsErrors" dxfId="36" priority="71">
+    <cfRule type="containsErrors" dxfId="18" priority="71">
       <formula>ISERROR(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="containsText" dxfId="35" priority="70" operator="containsText" text="rule">
+    <cfRule type="containsText" dxfId="17" priority="70" operator="containsText" text="rule">
       <formula>NOT(ISERROR(SEARCH("rule",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:C8">
-    <cfRule type="endsWith" dxfId="34" priority="68" operator="endsWith" text="rule">
+    <cfRule type="endsWith" dxfId="16" priority="68" operator="endsWith" text="rule">
       <formula>RIGHT(B8,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="notContainsBlanks" dxfId="33" priority="67">
+    <cfRule type="notContainsBlanks" dxfId="15" priority="67">
       <formula>LEN(TRIM(B9))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:C10">
-    <cfRule type="notContainsErrors" dxfId="32" priority="66">
+    <cfRule type="notContainsErrors" dxfId="14" priority="66">
       <formula>NOT(ISERROR(B10))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:C11">
-    <cfRule type="notContainsText" dxfId="31" priority="65" operator="notContains" text="rule">
+    <cfRule type="notContainsText" dxfId="13" priority="65" operator="notContains" text="rule">
       <formula>ISERROR(SEARCH("rule",B11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:C12">
-    <cfRule type="timePeriod" dxfId="30" priority="64" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="12" priority="64" timePeriod="today">
       <formula>FLOOR(B12,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="top10" dxfId="29" priority="116" percent="1" bottom="1" rank="50"/>
+    <cfRule type="top10" dxfId="11" priority="116" percent="1" bottom="1" rank="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:C16">
-    <cfRule type="cellIs" dxfId="28" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="46" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:C17">
-    <cfRule type="cellIs" dxfId="27" priority="57" operator="notEqual">
+    <cfRule type="cellIs" dxfId="9" priority="57" operator="notEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:C18">
-    <cfRule type="cellIs" dxfId="26" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:C20">
-    <cfRule type="cellIs" dxfId="24" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:C21">
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22">
-    <cfRule type="cellIs" dxfId="22" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="between">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="notBetween">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="notBetween">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
@@ -15344,16 +15235,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29:C29">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="between">
       <formula>$B$23</formula>
       <formula>2+2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D7">
-    <cfRule type="duplicateValues" dxfId="19" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D14">
-    <cfRule type="uniqueValues" dxfId="18" priority="97"/>
+    <cfRule type="uniqueValues" dxfId="0" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:J2">
     <cfRule type="colorScale" priority="45">
@@ -15776,7 +15667,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCC4B1-5C65-4837-AA26-56CCF06B63BB}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" customWidth="1"/>
@@ -15788,23 +15679,12 @@
     <col min="10" max="10" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="110" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>385</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-    </row>
-    <row r="3" spans="1:10" ht="15">
-      <c r="A3" s="110"/>
-      <c r="B3" s="110"/>
+    </row>
+    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="C3" s="17" t="s">
         <v>35</v>
       </c>
@@ -15830,9 +15710,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="110"/>
-      <c r="B4" s="110"/>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C4" s="109" t="s">
         <v>42</v>
       </c>
@@ -15863,9 +15741,7 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="110"/>
-      <c r="B5" s="110"/>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C5" s="109" t="s">
         <v>44</v>
       </c>
@@ -15896,9 +15772,7 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="110"/>
-      <c r="B6" s="110"/>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C6" s="109" t="s">
         <v>392</v>
       </c>
@@ -15931,254 +15805,212 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
         <v>393</v>
       </c>
-      <c r="C8" s="110">
-        <v>1</v>
-      </c>
-      <c r="D8" s="110">
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
         <v>2</v>
       </c>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110" t="s">
+      <c r="F8" t="s">
         <v>394</v>
       </c>
-      <c r="G8" s="110" t="s">
+      <c r="G8" t="s">
         <v>395</v>
       </c>
-      <c r="H8" s="110" t="s">
+      <c r="H8" t="s">
         <v>396</v>
       </c>
-      <c r="I8" s="110" t="s">
+      <c r="I8" t="s">
         <v>397</v>
       </c>
-      <c r="J8" s="110" t="s">
+      <c r="J8" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="110"/>
-      <c r="B9" s="110"/>
-      <c r="C9" s="110">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C9">
         <v>3</v>
       </c>
-      <c r="D9" s="110">
+      <c r="D9">
         <v>4</v>
       </c>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110">
+      <c r="F9">
         <f>SUM(Table3[#All])</f>
         <v>396</v>
       </c>
-      <c r="G9" s="110">
+      <c r="G9">
         <f>SUM(Table10[Col2])</f>
         <v>15</v>
       </c>
-      <c r="H9" s="110">
+      <c r="H9">
         <f>SUM(Table3[[#Totals],[Age]:[Rank]])</f>
         <v>51</v>
       </c>
-      <c r="I9" s="110">
+      <c r="I9">
         <f>SUM(Table3[[Age]:[Rank]])</f>
         <v>51</v>
       </c>
-      <c r="J9" s="110">
+      <c r="J9">
         <f>SUM(Table3[[#Data],[#Totals],[Rank]])</f>
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="110"/>
-      <c r="B11" s="110" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
         <v>399</v>
       </c>
-      <c r="C11" s="110" t="s">
+      <c r="C11" t="s">
         <v>400</v>
       </c>
-      <c r="D11" s="110" t="s">
+      <c r="D11" t="s">
         <v>401</v>
       </c>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="110"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="110"/>
-      <c r="B12" s="110"/>
-      <c r="C12" s="110">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C12">
         <v>3</v>
       </c>
-      <c r="D12" s="110">
+      <c r="D12">
         <v>4</v>
       </c>
-      <c r="E12" s="110"/>
-      <c r="F12" s="110"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="110"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="110"/>
-      <c r="B14" s="110" t="s">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
         <v>402</v>
       </c>
-      <c r="C14" s="110">
-        <v>1</v>
-      </c>
-      <c r="D14" s="110">
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
         <v>2</v>
       </c>
-      <c r="E14" s="110"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="110"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="110"/>
-      <c r="B15" s="110"/>
-      <c r="C15" s="110">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C15">
         <v>3</v>
       </c>
-      <c r="D15" s="110">
+      <c r="D15">
         <v>4</v>
       </c>
-      <c r="E15" s="110"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
-      <c r="I15" s="110"/>
-      <c r="J15" s="110"/>
-    </row>
-    <row r="17" spans="2:4">
-      <c r="B17" s="110" t="s">
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
         <v>403</v>
       </c>
-      <c r="C17" s="110">
-        <v>1</v>
-      </c>
-      <c r="D17" s="110">
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:4">
-      <c r="B18" s="110"/>
-      <c r="C18" s="110">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C18">
         <v>3</v>
       </c>
-      <c r="D18" s="110">
+      <c r="D18">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
-      <c r="B20" s="110" t="s">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
         <v>404</v>
       </c>
-      <c r="C20" s="110">
-        <v>1</v>
-      </c>
-      <c r="D20" s="110">
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:4">
-      <c r="B21" s="110"/>
-      <c r="C21" s="110">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C21">
         <v>3</v>
       </c>
-      <c r="D21" s="110">
+      <c r="D21">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
-      <c r="B23" s="110" t="s">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
         <v>405</v>
       </c>
-      <c r="C23" s="110">
-        <v>1</v>
-      </c>
-      <c r="D23" s="110">
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:4">
-      <c r="B24" s="110"/>
-      <c r="C24" s="110">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C24">
         <v>3</v>
       </c>
-      <c r="D24" s="110">
+      <c r="D24">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:4">
-      <c r="B26" s="110" t="s">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
         <v>406</v>
       </c>
-      <c r="C26" s="110">
-        <v>1</v>
-      </c>
-      <c r="D26" s="110">
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:4">
-      <c r="B27" s="110"/>
-      <c r="C27" s="110">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C27">
         <v>3</v>
       </c>
-      <c r="D27" s="110">
+      <c r="D27">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="2:4">
-      <c r="B28" s="110"/>
-      <c r="C28" s="110" t="s">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C28" t="s">
         <v>392</v>
       </c>
-      <c r="D28" s="110">
+      <c r="D28">
         <f>SUBTOTAL(109,Table4910[Column2])</f>
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="2:4">
-      <c r="B30" s="110" t="s">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
         <v>407</v>
       </c>
-      <c r="C30" s="110" t="s">
+      <c r="C30" t="s">
         <v>408</v>
       </c>
-      <c r="D30" s="110" t="s">
+      <c r="D30" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="31" spans="2:4" hidden="1">
-      <c r="B31" s="110"/>
-      <c r="C31" s="110" t="s">
+    <row r="31" spans="2:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="C31" t="s">
         <v>410</v>
       </c>
-      <c r="D31" s="110" t="s">
+      <c r="D31" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="32" spans="2:4">
-      <c r="B32" s="110"/>
-      <c r="C32" s="110" t="s">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C32" t="s">
         <v>411</v>
       </c>
-      <c r="D32" s="110" t="s">
+      <c r="D32" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="110" t="s">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
         <v>412</v>
       </c>
     </row>
@@ -16202,7 +16034,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9224F2-4D06-4586-886C-E51F5EBCA7B0}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -16223,7 +16055,7 @@
     <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15">
+    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="92" t="s">
         <v>413</v>
       </c>
@@ -16232,28 +16064,16 @@
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
       <c r="F1" s="17"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-    </row>
-    <row r="2" spans="1:12" ht="14.1">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="109"/>
       <c r="B2" s="109"/>
       <c r="C2" s="109"/>
       <c r="D2" s="109"/>
       <c r="E2" s="109"/>
       <c r="F2" s="109"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110"/>
-      <c r="K2" s="110"/>
-      <c r="L2" s="110"/>
-    </row>
-    <row r="3" spans="1:12" ht="14.1">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="109"/>
       <c r="B3" s="109"/>
       <c r="C3" s="89" t="s">
@@ -16262,390 +16082,258 @@
       <c r="D3" s="89" t="s">
         <v>415</v>
       </c>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="110"/>
-    </row>
-    <row r="4" spans="1:12" ht="14.1">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="109"/>
       <c r="B4" s="109"/>
       <c r="C4" s="89" t="s">
         <v>416</v>
       </c>
-      <c r="D4" s="110">
+      <c r="D4">
         <v>12.1</v>
       </c>
-      <c r="E4" s="110">
+      <c r="E4">
         <v>252.4</v>
       </c>
-      <c r="F4" s="110">
+      <c r="F4">
         <v>500.9</v>
       </c>
-      <c r="G4" s="110">
+      <c r="G4">
         <v>1204.7</v>
       </c>
-      <c r="H4" s="110">
+      <c r="H4">
         <v>4000</v>
       </c>
-      <c r="I4" s="110">
+      <c r="I4">
         <v>4701.3</v>
       </c>
-      <c r="J4" s="110">
+      <c r="J4">
         <v>4890.1000000000004</v>
       </c>
-      <c r="K4" s="110">
+      <c r="K4">
         <v>12052</v>
       </c>
-      <c r="L4" s="110" t="s">
+      <c r="L4" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="14.1">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="109"/>
       <c r="B5" s="109"/>
       <c r="C5" s="90" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="110">
+      <c r="K5">
         <v>30</v>
       </c>
-      <c r="L5" s="110">
+      <c r="L5">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="14.1">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="109"/>
       <c r="B6" s="109"/>
       <c r="C6" s="91">
         <v>256018</v>
       </c>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="110"/>
-      <c r="K6" s="110">
+      <c r="K6">
         <v>30</v>
       </c>
-      <c r="L6" s="110">
+      <c r="L6">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="14.1">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="109"/>
       <c r="B7" s="109"/>
       <c r="C7" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110">
+      <c r="E7">
         <v>26</v>
       </c>
-      <c r="F7" s="110"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="110"/>
-      <c r="L7" s="110">
+      <c r="L7">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="14.1">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="109"/>
       <c r="B8" s="109"/>
       <c r="C8" s="91">
         <v>110120.5</v>
       </c>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110">
+      <c r="E8">
         <v>26</v>
       </c>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="110"/>
-      <c r="L8" s="110">
+      <c r="L8">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="14.1">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="109"/>
       <c r="B9" s="109"/>
       <c r="C9" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="110"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="110">
+      <c r="G9">
         <v>26</v>
       </c>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="110"/>
-      <c r="K9" s="110"/>
-      <c r="L9" s="110">
+      <c r="L9">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="14.1">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="109"/>
       <c r="B10" s="109"/>
       <c r="C10" s="91">
         <v>25618</v>
       </c>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110">
+      <c r="G10">
         <v>26</v>
       </c>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="110">
+      <c r="L10">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="14.1">
-      <c r="A11" s="110"/>
-      <c r="B11" s="110"/>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110">
+      <c r="F11">
         <v>13</v>
       </c>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="110"/>
-      <c r="K11" s="110"/>
-      <c r="L11" s="110">
+      <c r="L11">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="14.1">
-      <c r="A12" s="110"/>
-      <c r="B12" s="110"/>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="91">
         <v>23000</v>
       </c>
-      <c r="D12" s="110"/>
-      <c r="E12" s="110"/>
-      <c r="F12" s="110">
+      <c r="F12">
         <v>13</v>
       </c>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="110"/>
-      <c r="K12" s="110"/>
-      <c r="L12" s="110">
+      <c r="L12">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="14.1">
-      <c r="A13" s="110"/>
-      <c r="B13" s="110"/>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="90" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="110">
+      <c r="D13">
         <v>9</v>
       </c>
-      <c r="E13" s="110"/>
-      <c r="F13" s="110"/>
-      <c r="G13" s="110"/>
-      <c r="H13" s="110"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="110"/>
-      <c r="K13" s="110"/>
-      <c r="L13" s="110">
+      <c r="L13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="14.1">
-      <c r="A14" s="110"/>
-      <c r="B14" s="110"/>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="91">
         <v>2</v>
       </c>
-      <c r="D14" s="110">
+      <c r="D14">
         <v>9</v>
       </c>
-      <c r="E14" s="110"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="110"/>
-      <c r="L14" s="110">
+      <c r="L14">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="14.1">
-      <c r="A15" s="110"/>
-      <c r="B15" s="110"/>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="110"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
-      <c r="I15" s="110">
+      <c r="I15">
         <v>42</v>
       </c>
-      <c r="J15" s="110"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="110">
+      <c r="L15">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="14.1">
-      <c r="A16" s="110"/>
-      <c r="B16" s="110"/>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C16" s="91">
         <v>50024</v>
       </c>
-      <c r="D16" s="110"/>
-      <c r="E16" s="110"/>
-      <c r="F16" s="110"/>
-      <c r="G16" s="110"/>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110">
+      <c r="I16">
         <v>42</v>
       </c>
-      <c r="J16" s="110"/>
-      <c r="K16" s="110"/>
-      <c r="L16" s="110">
+      <c r="L16">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="3:12" ht="14.1">
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="110"/>
-      <c r="E17" s="110"/>
-      <c r="F17" s="110"/>
-      <c r="G17" s="110"/>
-      <c r="H17" s="110">
+      <c r="H17">
         <v>27</v>
       </c>
-      <c r="I17" s="110"/>
-      <c r="J17" s="110"/>
-      <c r="K17" s="110"/>
-      <c r="L17" s="110">
+      <c r="L17">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="3:12" ht="14.1">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="91">
         <v>189576</v>
       </c>
-      <c r="D18" s="110"/>
-      <c r="E18" s="110"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110">
+      <c r="H18">
         <v>27</v>
       </c>
-      <c r="I18" s="110"/>
-      <c r="J18" s="110"/>
-      <c r="K18" s="110"/>
-      <c r="L18" s="110">
+      <c r="L18">
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="3:12" ht="14.1">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="110"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110">
+      <c r="J19">
         <v>37</v>
       </c>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110">
+      <c r="L19">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="3:12" ht="14.1">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="91">
         <v>5000</v>
       </c>
-      <c r="D20" s="110"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="110"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110">
+      <c r="J20">
         <v>37</v>
       </c>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110">
+      <c r="L20">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="3:12" ht="14.1">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="90" t="s">
         <v>417</v>
       </c>
-      <c r="D21" s="110">
+      <c r="D21">
         <v>9</v>
       </c>
-      <c r="E21" s="110">
+      <c r="E21">
         <v>26</v>
       </c>
-      <c r="F21" s="110">
+      <c r="F21">
         <v>13</v>
       </c>
-      <c r="G21" s="110">
+      <c r="G21">
         <v>26</v>
       </c>
-      <c r="H21" s="110">
+      <c r="H21">
         <v>27</v>
       </c>
-      <c r="I21" s="110">
+      <c r="I21">
         <v>42</v>
       </c>
-      <c r="J21" s="110">
+      <c r="J21">
         <v>37</v>
       </c>
-      <c r="K21" s="110">
+      <c r="K21">
         <v>30</v>
       </c>
-      <c r="L21" s="110">
+      <c r="L21">
         <v>210</v>
       </c>
     </row>
@@ -16658,35 +16346,32 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="110" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>418</v>
       </c>
-      <c r="B1" s="110"/>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="110" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>419</v>
       </c>
       <c r="B2" s="109"/>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="110" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>420</v>
       </c>
-      <c r="B3" s="110"/>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="110" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>421</v>
       </c>
-      <c r="B4" s="110"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16697,61 +16382,61 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE31E21-0350-44E7-AF13-4CA140505B30}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="51">
+    <row r="1" spans="1:2" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
         <v>422</v>
       </c>
-      <c r="B1" s="110" t="s">
+      <c r="B1" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="110" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>408</v>
       </c>
-      <c r="B7" s="110" t="s">
+      <c r="B7" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="110">
-        <v>1</v>
-      </c>
-      <c r="B8" s="110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="110">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>2</v>
       </c>
-      <c r="B9" s="110">
+      <c r="B9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="110">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>3</v>
       </c>
-      <c r="B10" s="110">
+      <c r="B10">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="110">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
         <v>4</v>
       </c>
-      <c r="B11" s="110">
+      <c r="B11">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="110">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
         <v>5</v>
       </c>
-      <c r="B12" s="110">
+      <c r="B12">
         <v>5</v>
       </c>
     </row>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rar/rar-workspace/o-spreadsheet/tests/__xlsx__/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C7959D-379F-564A-B7D4-13925F876C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55875EC-6DA4-4B3F-81BC-027B883C599F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23400" yWindow="2720" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,10 +32,11 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId17"/>
+    <externalReference r:id="rId18"/>
   </externalReferences>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId18"/>
+    <pivotCache cacheId="0" r:id="rId19"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2818,7 +2819,7 @@
         <u/>
         <color theme="7"/>
       </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
       <fill>
         <patternFill patternType="lightTrellis">
           <fgColor theme="4"/>
@@ -2986,7 +2987,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3603,7 +3604,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3966,7 +3967,515 @@
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2200"/>
+              <a:t>chart with composite ranges</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>([2]Sheet1!$A$27:$C$35,[2]Sheet1!$A$27:$C$31)</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>24</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>27</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>45</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>17</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>43</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>11</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>16</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>24</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>27</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>45</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>48</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>45</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>25</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>31</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>20</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>19</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>16</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>48</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>45</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>25</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Emily Anderson (Emmy)</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Sophie Allen (Saffi)</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Chloe Adams</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Megan Alexander (Meg)</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lucy Arnold (Lulu)</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Hannah Alvarez</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Jessica Alcock (Jess)</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Charlotte Anaya</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lauren Anthony</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Emily Anderson (Emmy)</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Sophie Allen (Saffi)</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Chloe Adams</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Megan Alexander (Meg)</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lucy Arnold (Lulu)</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[2]Sheet1!$B$27:$B$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="7030A0"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8580-4F31-80CD-FFF44C07CE87}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C65911"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="C65911"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>[2]Sheet1!$A$27:$A$31</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[2]Sheet1!$C$27:$C$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="C65911"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8580-4F31-80CD-FFF44C07CE87}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="70"/>
+        <c:overlap val="-20"/>
+        <c:axId val="17781237"/>
+        <c:axId val="88853993"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="17781237"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="1000" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="88853993"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="88853993"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="1000" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="17781237"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr sz="1000" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln cmpd="sng">
+      <a:solidFill>
+        <a:srgbClr val="000000"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -4382,7 +4891,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4848,7 +5357,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -5466,7 +5975,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5832,7 +6341,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -6144,7 +6653,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6575,7 +7084,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6977,7 +7486,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7280,7 +7789,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8647,6 +9156,47 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Chart 11" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7F7EAE9-743A-4FFF-8E63-2D93C41C22EF}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8771,6 +9321,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Feuil1"/>
     </sheetNames>
@@ -8782,6 +9335,149 @@
           </cell>
         </row>
       </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Formulas"/>
+      <sheetName val="jestSheet"/>
+      <sheetName val="jestStyles"/>
+      <sheetName val="jestCfs"/>
+      <sheetName val="jestTable"/>
+      <sheetName val="jestPivot"/>
+      <sheetName val="jestCharts"/>
+      <sheetName val="jestMiscTest"/>
+      <sheetName val="jestHiddenSheet"/>
+      <sheetName val="jestFreezePane"/>
+      <sheetName val="jestImages"/>
+      <sheetName val="jestOneCellAnchor"/>
+      <sheetName val="jestDataValidations"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="27">
+          <cell r="A27" t="str">
+            <v>Emily Anderson (Emmy)</v>
+          </cell>
+          <cell r="B27">
+            <v>12</v>
+          </cell>
+          <cell r="C27">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28" t="str">
+            <v>Sophie Allen (Saffi)</v>
+          </cell>
+          <cell r="B28">
+            <v>48</v>
+          </cell>
+          <cell r="C28">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29" t="str">
+            <v>Chloe Adams</v>
+          </cell>
+          <cell r="B29">
+            <v>45</v>
+          </cell>
+          <cell r="C29">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>Megan Alexander (Meg)</v>
+          </cell>
+          <cell r="B30">
+            <v>1</v>
+          </cell>
+          <cell r="C30">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31" t="str">
+            <v>Lucy Arnold (Lulu)</v>
+          </cell>
+          <cell r="B31">
+            <v>25</v>
+          </cell>
+          <cell r="C31">
+            <v>45</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32" t="str">
+            <v>Hannah Alvarez</v>
+          </cell>
+          <cell r="B32">
+            <v>31</v>
+          </cell>
+          <cell r="C32">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33" t="str">
+            <v>Jessica Alcock (Jess)</v>
+          </cell>
+          <cell r="B33">
+            <v>20</v>
+          </cell>
+          <cell r="C33">
+            <v>43</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34" t="str">
+            <v>Charlotte Anaya</v>
+          </cell>
+          <cell r="B34">
+            <v>19</v>
+          </cell>
+          <cell r="C34">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35" t="str">
+            <v>Lauren Anthony</v>
+          </cell>
+          <cell r="B35">
+            <v>16</v>
+          </cell>
+          <cell r="C35">
+            <v>16</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -9504,13 +10200,13 @@
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.19921875" customWidth="1"/>
-    <col min="2" max="2" width="13.796875" customWidth="1"/>
-    <col min="3" max="3" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.19921875" customWidth="1"/>
-    <col min="6" max="26" width="13.796875" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="26" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9522,7 +10218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="27.75" x14ac:dyDescent="0.2">
       <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
@@ -9949,7 +10645,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9958,7 +10654,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9967,10 +10663,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="65.19921875" customWidth="1"/>
-    <col min="2" max="26" width="13.796875" customWidth="1"/>
+    <col min="1" max="1" width="65.140625" customWidth="1"/>
+    <col min="2" max="26" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9984,7 +10680,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -9994,13 +10690,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025F2510-D243-4DA1-81DE-BBDDA9BC3681}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="4" width="14.19921875" customWidth="1"/>
-    <col min="5" max="5" width="14.796875" customWidth="1"/>
-    <col min="7" max="7" width="14.19921875" customWidth="1"/>
-    <col min="8" max="8" width="20.19921875" customWidth="1"/>
-    <col min="9" max="9" width="17.19921875" customWidth="1"/>
+    <col min="3" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="20.140625" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" customWidth="1"/>
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10241,7 +10937,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{175FB5D6-D3ED-FD4F-886B-71BD0CB28755}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10251,7 +10947,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B936FE7B-5147-E945-A711-7FBABD0575D3}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10264,9 +10960,9 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:R163"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="26" width="13.796875" customWidth="1"/>
+    <col min="1" max="26" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12117,7 +12813,7 @@
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>46050.431470138887</v>
+        <v>46316.610532175924</v>
       </c>
       <c r="D100" s="104">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
@@ -12807,7 +13503,7 @@
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>46050</v>
+        <v>46316</v>
       </c>
       <c r="D144" s="104">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
@@ -13139,14 +13835,14 @@
     <outlinePr summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.19921875" customWidth="1"/>
-    <col min="10" max="10" width="9.19921875" outlineLevel="1"/>
-    <col min="11" max="11" width="9.19921875" outlineLevel="1" collapsed="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" outlineLevel="1"/>
+    <col min="11" max="11" width="9.140625" outlineLevel="1" collapsed="1"/>
     <col min="12" max="14" width="0" hidden="1" outlineLevel="2"/>
-    <col min="15" max="18" width="9.19921875" outlineLevel="1"/>
+    <col min="15" max="18" width="9.140625" outlineLevel="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -13209,21 +13905,21 @@
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" cm="1">
         <f t="array" aca="1" ref="A30:B31" ca="1">_xlfn.RANDARRAY(2,2)</f>
-        <v>0.77093979243831789</v>
+        <v>0.78372052454907659</v>
       </c>
       <c r="B30">
         <f ca="1"/>
-        <v>0.89996963625071968</v>
+        <v>5.8539393828227926E-2</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
         <f ca="1"/>
-        <v>4.753041610255937E-2</v>
+        <v>0.53144097201098628</v>
       </c>
       <c r="B31">
         <f ca="1"/>
-        <v>0.61224139121963739</v>
+        <v>0.99378707129168786</v>
       </c>
     </row>
   </sheetData>
@@ -13242,14 +13938,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF68F2C0-1053-4FB6-BD74-8A11B0CAF123}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="17.796875" customWidth="1"/>
-    <col min="5" max="5" width="18.19921875" customWidth="1"/>
-    <col min="13" max="13" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="68" t="s">
         <v>239</v>
       </c>
@@ -13320,7 +14016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="42" t="s">
         <v>256</v>
       </c>
@@ -13389,7 +14085,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="45" t="s">
         <v>271</v>
       </c>
@@ -13409,7 +14105,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.35">
       <c r="A8" s="46" t="s">
         <v>275</v>
       </c>
@@ -13432,7 +14128,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="47" t="s">
         <v>280</v>
       </c>
@@ -13457,7 +14153,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="49" t="s">
         <v>285</v>
       </c>
@@ -13530,12 +14226,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="55" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="74" t="s">
         <v>297</v>
       </c>
@@ -13547,7 +14243,7 @@
       </c>
       <c r="F18" s="36"/>
     </row>
-    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="75" t="s">
         <v>300</v>
       </c>
@@ -13558,7 +14254,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="61" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="76" t="s">
         <v>303</v>
       </c>
@@ -13572,12 +14268,12 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="77" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="78" t="s">
         <v>307</v>
       </c>
@@ -13586,13 +14282,13 @@
       </c>
       <c r="E22" s="21"/>
     </row>
-    <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="79" t="s">
         <v>309</v>
       </c>
       <c r="E23" s="21"/>
     </row>
-    <row r="24" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="80" t="s">
         <v>310</v>
       </c>
@@ -13601,19 +14297,19 @@
       </c>
       <c r="E24" s="21"/>
     </row>
-    <row r="25" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C26" s="67" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:6" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C28" s="88" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C30" s="87" t="s">
         <v>314</v>
@@ -13628,13 +14324,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919E811-4385-4D35-A19E-3B7E0E659A89}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.19921875" customWidth="1"/>
-    <col min="7" max="7" width="15.796875" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
         <v>315</v>
       </c>
@@ -13810,7 +14506,7 @@
       </c>
       <c r="C9" s="21"/>
     </row>
-    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="38" t="s">
         <v>340</v>
       </c>
@@ -13857,7 +14553,7 @@
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>46050</v>
+        <v>46316</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
@@ -14296,7 +14992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G31" s="35" t="s">
         <v>378</v>
       </c>
@@ -14963,16 +15659,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCC4B1-5C65-4837-AA26-56CCF06B63BB}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="17.19921875" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" customWidth="1"/>
-    <col min="5" max="5" width="26.3984375" customWidth="1"/>
-    <col min="6" max="6" width="27.59765625" customWidth="1"/>
-    <col min="7" max="7" width="23.59765625" customWidth="1"/>
-    <col min="8" max="8" width="16.19921875" customWidth="1"/>
-    <col min="9" max="9" width="18.796875" customWidth="1"/>
-    <col min="10" max="10" width="17.19921875" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" customWidth="1"/>
+    <col min="6" max="6" width="27.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -14980,7 +15676,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="C3" s="17" t="s">
         <v>35</v>
       </c>
@@ -15330,28 +16026,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9224F2-4D06-4586-886C-E51F5EBCA7B0}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.19921875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="92" t="s">
         <v>413</v>
       </c>
@@ -15361,7 +16057,7 @@
       <c r="E1" s="17"/>
       <c r="F1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A2" s="104"/>
       <c r="B2" s="104"/>
       <c r="C2" s="104"/>
@@ -15369,7 +16065,7 @@
       <c r="E2" s="104"/>
       <c r="F2" s="104"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A3" s="104"/>
       <c r="B3" s="104"/>
       <c r="C3" s="89" t="s">
@@ -15379,7 +16075,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A4" s="104"/>
       <c r="B4" s="104"/>
       <c r="C4" s="89" t="s">
@@ -15413,7 +16109,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A5" s="104"/>
       <c r="B5" s="104"/>
       <c r="C5" s="90" t="s">
@@ -15426,7 +16122,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A6" s="104"/>
       <c r="B6" s="104"/>
       <c r="C6" s="91">
@@ -15439,7 +16135,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A7" s="104"/>
       <c r="B7" s="104"/>
       <c r="C7" s="90" t="s">
@@ -15452,7 +16148,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A8" s="104"/>
       <c r="B8" s="104"/>
       <c r="C8" s="91">
@@ -15465,7 +16161,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A9" s="104"/>
       <c r="B9" s="104"/>
       <c r="C9" s="90" t="s">
@@ -15478,7 +16174,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="A10" s="104"/>
       <c r="B10" s="104"/>
       <c r="C10" s="91">
@@ -15491,7 +16187,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C11" s="90" t="s">
         <v>44</v>
       </c>
@@ -15502,7 +16198,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C12" s="91">
         <v>23000</v>
       </c>
@@ -15513,7 +16209,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C13" s="90" t="s">
         <v>50</v>
       </c>
@@ -15524,7 +16220,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C14" s="91">
         <v>2</v>
       </c>
@@ -15535,7 +16231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C15" s="90" t="s">
         <v>48</v>
       </c>
@@ -15546,7 +16242,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C16" s="91">
         <v>50024</v>
       </c>
@@ -15557,7 +16253,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C17" s="90" t="s">
         <v>53</v>
       </c>
@@ -15568,7 +16264,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C18" s="91">
         <v>189576</v>
       </c>
@@ -15579,7 +16275,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C19" s="90" t="s">
         <v>57</v>
       </c>
@@ -15590,7 +16286,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C20" s="91">
         <v>5000</v>
       </c>
@@ -15601,7 +16297,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" ht="14.1" x14ac:dyDescent="0.2">
       <c r="C21" s="90" t="s">
         <v>417</v>
       </c>
@@ -15642,10 +16338,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="65.19921875" customWidth="1"/>
-    <col min="2" max="26" width="13.796875" customWidth="1"/>
+    <col min="1" max="1" width="65.140625" customWidth="1"/>
+    <col min="2" max="26" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -15678,9 +16374,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE31E21-0350-44E7-AF13-4CA140505B30}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
         <v>422</v>
       </c>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dhrutik Patel\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B86E9B1-DF37-4B7C-B14C-0625DAE1CA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CD15DC-0D5B-4399-A5B2-1B9193AA1001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,9 @@
   <externalReferences>
     <externalReference r:id="rId15"/>
   </externalReferences>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="4560" r:id="rId16"/>
+    <pivotCache cacheId="0" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1415,7 +1415,7 @@
     <numFmt numFmtId="168" formatCode="#,##0&quot; EUR €&quot;"/>
     <numFmt numFmtId="169" formatCode="&quot;€&quot;#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2415,6 +2415,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2427,165 +2428,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1493241F-B85D-4F84-BBA0-86191B8FD032}"/>
   </cellStyles>
   <dxfs count="47">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <strike/>
-        <u/>
-        <color theme="7"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="lightTrellis">
-          <fgColor theme="4"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2999,6 +2848,157 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike/>
+        <u/>
+        <color theme="7"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="lightTrellis">
+          <fgColor theme="4"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE06666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB6D7A8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
@@ -3042,7 +3042,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3640,10 +3640,426 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>first dataset</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hannah Alvarez</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jessica Alcock (Jess)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Charlotte Anaya</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Lauren Anthony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$27:$B$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>second dataset</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hannah Alvarez</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jessica Alcock (Jess)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Charlotte Anaya</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Lauren Anthony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$27:$C$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln cmpd="sng">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="998664793"/>
+        <c:axId val="344680958"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="998664793"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="344680958"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="344680958"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="998664793"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4075,7 +4491,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4693,7 +5109,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5059,7 +5475,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -5358,7 +5774,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5775,7 +6191,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6177,7 +6593,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6467,47 +6883,67 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2200"/>
+              <a:t>chart with composite ranges</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="1"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$B$26</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>first dataset</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4472C4"/>
+              <a:srgbClr val="7030A0"/>
             </a:solidFill>
-            <a:ln cmpd="sng">
+            <a:ln>
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:f>Sheet1!$A$27:$C$35,Sheet1!$A$27:$C$31</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>Emily Anderson (Emmy)</c:v>
                 </c:pt>
@@ -6522,28 +6958,16 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Lucy Arnold (Lulu)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Hannah Alvarez</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Jessica Alcock (Jess)</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Charlotte Anaya</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Lauren Anthony</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$27:$B$35</c:f>
+              <c:f>Sheet1!$B$27:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>12</c:v>
                 </c:pt>
@@ -6558,18 +6982,6 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6581,49 +6993,40 @@
                   <a:solidFill>
                     <a:srgbClr val="FFFFFF"/>
                   </a:solidFill>
-                  <a:ln cmpd="sng">
+                  <a:ln>
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="7030A0"/>
                     </a:solidFill>
+                    <a:prstDash val="solid"/>
                   </a:ln>
                 </c14:spPr>
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+              <c16:uniqueId val="{00000000-A7CB-4BB7-A9D8-9DA337DFF3C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$C$26</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>second dataset</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ED7D31"/>
+              <a:srgbClr val="C65911"/>
             </a:solidFill>
-            <a:ln cmpd="sng">
+            <a:ln>
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="C65911"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$27:$A$35</c:f>
+              <c:f>Sheet1!$A$27:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>Emily Anderson (Emmy)</c:v>
                 </c:pt>
@@ -6638,28 +7041,16 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Lucy Arnold (Lulu)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Hannah Alvarez</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Jessica Alcock (Jess)</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Charlotte Anaya</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Lauren Anthony</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$27:$C$35</c:f>
+              <c:f>Sheet1!$C$27:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>24</c:v>
                 </c:pt>
@@ -6674,18 +7065,6 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6697,16 +7076,17 @@
                   <a:solidFill>
                     <a:srgbClr val="FFFFFF"/>
                   </a:solidFill>
-                  <a:ln cmpd="sng">
+                  <a:ln>
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:srgbClr val="C65911"/>
                     </a:solidFill>
+                    <a:prstDash val="solid"/>
                   </a:ln>
                 </c14:spPr>
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D94B-45A0-8AD6-3E4F4E7665C2}"/>
+              <c16:uniqueId val="{00000001-A7CB-4BB7-A9D8-9DA337DFF3C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6718,17 +7098,27 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="998664793"/>
-        <c:axId val="344680958"/>
+        <c:gapWidth val="70"/>
+        <c:overlap val="-20"/>
+        <c:axId val="17781237"/>
+        <c:axId val="88853993"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="998664793"/>
+        <c:axId val="17781237"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -6743,14 +7133,14 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr/>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:txPr>
@@ -6758,7 +7148,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0">
+              <a:defRPr sz="1000" b="0" i="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -6768,7 +7158,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="344680958"/>
+        <c:crossAx val="88853993"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6776,7 +7166,7 @@
         <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="344680958"/>
+        <c:axId val="88853993"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6784,24 +7174,13 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln>
+            <a:ln cmpd="sng">
               <a:solidFill>
                 <a:srgbClr val="B7B7B7"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC">
-                  <a:alpha val="0"/>
-                </a:srgbClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -6816,25 +7195,22 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr/>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln/>
-        </c:spPr>
         <c:txPr>
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0">
+              <a:defRPr sz="1000" b="0" i="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -6844,10 +7220,15 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="998664793"/>
+        <c:crossAx val="17781237"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
@@ -6857,9 +7238,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr lvl="0">
-            <a:defRPr b="0">
+            <a:defRPr sz="1000" b="0" i="0">
               <a:solidFill>
-                <a:srgbClr val="1A1A1A"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
@@ -6872,6 +7253,16 @@
     <c:dispBlanksAs val="zero"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln cmpd="sng">
+      <a:solidFill>
+        <a:srgbClr val="000000"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -7675,6 +8066,47 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>904875</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 9" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E3EA9F7-57EC-48BF-B89B-57BA25057E90}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7937,7 +8369,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="4560" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -8087,7 +8519,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}" name="Table3" displayName="Table3" ref="C3:J6" totalsRowCount="1" headerRowDxfId="44" dataDxfId="43">
   <autoFilter ref="C3:J5" xr:uid="{09C35CC7-7259-4A97-8FEA-EDB47375DF08}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8099,22 +8531,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="14" totalsRowDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="9">
+    <tableColumn id="1" xr3:uid="{C4EE018E-238B-42BA-9035-DB01FA5420D3}" name="Name" totalsRowLabel="Total" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{C1F6911F-9482-4C98-BBFB-21D9CAA66DA4}" name="Age" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{3CE9F5DA-0A57-4696-B4E0-53601C3B7798}" name="Rank" totalsRowFunction="sum" dataDxfId="38" totalsRowDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{34912838-665C-4472-B558-25990E5B148D}" name="Rank+Age =E4+D4" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="35">
       <calculatedColumnFormula>Table3[[#This Row],[Rank]]+Table3[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="7">
+    <tableColumn id="7" xr3:uid="{89D90022-7073-4067-BAF8-1587D27C4AFB}" name="Data =SUM(E4:E5)" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="33">
       <calculatedColumnFormula>SUM(Table3[Rank])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="4" totalsRowDxfId="5">
+    <tableColumn id="8" xr3:uid="{B2A7E5BB-A379-492B-9484-72F2FD1FF3A0}" name="All =SUM(E3:E6)" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31">
       <calculatedColumnFormula>SUM(Table3[[#All],[Rank]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="2" totalsRowDxfId="3">
+    <tableColumn id="9" xr3:uid="{3C532A69-E4BC-4A20-A922-4BCAA0D3FEC9}" name="Totals =E6" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="29">
       <calculatedColumnFormula>Table3[[#Totals],[Rank]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="0" totalsRowDxfId="1">
+    <tableColumn id="10" xr3:uid="{35E9E9C3-9148-468A-85B6-19290CEB6F00}" name="Headers =E3" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="27">
       <calculatedColumnFormula>Table3[[#Headers],[Rank]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8235,9 +8667,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -8275,7 +8707,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -8381,7 +8813,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8523,7 +8955,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -8535,7 +8967,7 @@
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
@@ -8544,7 +8976,7 @@
     <col min="6" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" customHeight="1">
+    <row r="1" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -8553,7 +8985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="27.75">
+    <row r="2" spans="1:12" ht="27.75" x14ac:dyDescent="0.2">
       <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
@@ -8566,25 +8998,25 @@
       <c r="H2" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="123"/>
+      <c r="I2" s="119"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:12" ht="17.25" customHeight="1">
+    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="117">
         <v>8</v>
       </c>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="119">
+      <c r="K3" s="120">
         <v>5</v>
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="1:12" ht="17.25" customHeight="1">
+    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
@@ -8597,50 +9029,50 @@
       <c r="G4" s="117">
         <v>9</v>
       </c>
-      <c r="H4" s="123"/>
-      <c r="I4" s="123"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" ht="17.25" customHeight="1">
+    <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="117">
         <v>42</v>
       </c>
       <c r="G5" s="117">
         <v>15</v>
       </c>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="1:12" ht="17.25" customHeight="1">
+    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G6" s="117">
         <v>22</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="120"/>
+      <c r="K6" s="121"/>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="1:12" ht="17.25" customHeight="1">
+    <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="117">
         <v>3</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="120"/>
+      <c r="K7" s="121"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" ht="17.25" customHeight="1">
+    <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G8" s="117">
         <v>30</v>
       </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="121"/>
+      <c r="K8" s="122"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" ht="17.25" customHeight="1">
+    <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
@@ -8650,7 +9082,7 @@
       </c>
       <c r="K9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="17.25" customHeight="1">
+    <row r="10" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="117">
         <f>SUM(C4:C7)</f>
         <v>57.4</v>
@@ -8659,13 +9091,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="117">
         <f>-(3+C7*SUM(C4:C7))</f>
         <v>-175.2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17.25" customHeight="1">
+    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="117">
         <f>SUM(C9:C11)</f>
         <v>-63.399999999999991</v>
@@ -8674,13 +9106,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G13" s="117">
         <f>A1+A2+A3+A4+A5+A6+A7+A8+A9+A10+A11+A12+A13+A14+A15+A16+A17+A18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17.25" customHeight="1">
+    <row r="14" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
@@ -8689,32 +9121,32 @@
         <v>#CYCLE</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17.25" customHeight="1">
+    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="117" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17.25" customHeight="1">
+    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" s="117" t="str">
         <f>C15</f>
         <v>=(+</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17.25" customHeight="1">
+    <row r="17" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="117" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17.25" customHeight="1">
+    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="117" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="17.25" customHeight="1">
+    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E19" s="3"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:9" ht="17.25" customHeight="1">
+    <row r="20" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="5"/>
       <c r="C20" s="6" t="s">
         <v>15</v>
@@ -8728,7 +9160,7 @@
       </c>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:9" ht="17.25" customHeight="1">
+    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
         <v>18</v>
       </c>
@@ -8738,7 +9170,7 @@
       </c>
       <c r="G21" s="10"/>
     </row>
-    <row r="23" spans="1:9" ht="17.25" customHeight="1">
+    <row r="23" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="13" t="s">
         <v>19</v>
       </c>
@@ -8752,7 +9184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17.25" customHeight="1">
+    <row r="24" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="16">
         <v>10</v>
       </c>
@@ -8763,7 +9195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17.25" customHeight="1">
+    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="16">
         <v>10.122999999999999</v>
       </c>
@@ -8774,7 +9206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17.25" customHeight="1">
+    <row r="26" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="117" t="s">
         <v>20</v>
       </c>
@@ -8788,7 +9220,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17.25" customHeight="1">
+    <row r="27" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="117" t="s">
         <v>22</v>
       </c>
@@ -8805,7 +9237,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17.25" customHeight="1">
+    <row r="28" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="117" t="s">
         <v>23</v>
       </c>
@@ -8822,7 +9254,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17.25" customHeight="1">
+    <row r="29" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="117" t="s">
         <v>24</v>
       </c>
@@ -8839,7 +9271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17.25" customHeight="1">
+    <row r="30" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="117" t="s">
         <v>25</v>
       </c>
@@ -8856,7 +9288,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17.25" customHeight="1">
+    <row r="31" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="117" t="s">
         <v>26</v>
       </c>
@@ -8873,7 +9305,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17.25" customHeight="1">
+    <row r="32" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="117" t="s">
         <v>27</v>
       </c>
@@ -8890,7 +9322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17.25" customHeight="1">
+    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="117" t="s">
         <v>28</v>
       </c>
@@ -8907,7 +9339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17.25" customHeight="1">
+    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="117" t="s">
         <v>29</v>
       </c>
@@ -8918,7 +9350,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17.25" customHeight="1">
+    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="117" t="s">
         <v>30</v>
       </c>
@@ -8935,7 +9367,7 @@
     <mergeCell ref="K3:K8"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C100 B21">
-    <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>42</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8980,7 +9412,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7A934C-2218-4A12-8B75-EE28D615D774}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8989,7 +9421,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96301BE1-D86D-4D45-870D-85A75D53FC99}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8998,7 +9430,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10A8834-0E20-4F80-8813-3ACA5527B377}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
@@ -9015,7 +9447,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -9025,7 +9457,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025F2510-D243-4DA1-81DE-BBDDA9BC3681}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
@@ -9034,7 +9466,7 @@
     <col min="9" max="9" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="114" t="s">
         <v>424</v>
       </c>
@@ -9063,7 +9495,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="104">
         <v>4</v>
       </c>
@@ -9095,7 +9527,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="104">
         <v>3</v>
       </c>
@@ -9127,7 +9559,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="104">
         <v>9</v>
       </c>
@@ -9159,7 +9591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="104">
         <v>5</v>
       </c>
@@ -9191,7 +9623,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="109">
         <v>7</v>
       </c>
@@ -9271,12 +9703,12 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:R163"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17.25" customHeight="1">
+    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="117" t="s">
         <v>31</v>
       </c>
@@ -9311,7 +9743,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1">
+    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="117" t="s">
         <v>41</v>
       </c>
@@ -9357,7 +9789,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17.25" customHeight="1">
+    <row r="3" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="117" t="s">
         <v>43</v>
       </c>
@@ -9403,7 +9835,7 @@
         <v>1217.7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="17.25" customHeight="1">
+    <row r="4" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="117" t="s">
         <v>45</v>
       </c>
@@ -9449,7 +9881,7 @@
         <v>1230.7</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="17.25" customHeight="1">
+    <row r="5" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="117" t="s">
         <v>47</v>
       </c>
@@ -9495,7 +9927,7 @@
         <v>1246.7</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="17.25" customHeight="1">
+    <row r="6" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="117" t="s">
         <v>49</v>
       </c>
@@ -9541,7 +9973,7 @@
         <v>1213.7</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.25" customHeight="1">
+    <row r="7" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="117" t="s">
         <v>52</v>
       </c>
@@ -9575,7 +10007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="17.25" customHeight="1">
+    <row r="8" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="117" t="s">
         <v>54</v>
       </c>
@@ -9609,7 +10041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.25" customHeight="1">
+    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="117" t="s">
         <v>56</v>
       </c>
@@ -9640,7 +10072,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17.25" customHeight="1">
+    <row r="10" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="117" t="s">
         <v>58</v>
       </c>
@@ -9656,7 +10088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="17.25" customHeight="1">
+    <row r="11" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="117" t="s">
         <v>59</v>
       </c>
@@ -9675,7 +10107,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.25" customHeight="1">
+    <row r="12" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="117" t="s">
         <v>61</v>
       </c>
@@ -9706,7 +10138,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.25" customHeight="1">
+    <row r="13" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="117" t="s">
         <v>62</v>
       </c>
@@ -9737,7 +10169,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.25" customHeight="1">
+    <row r="14" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="117" t="s">
         <v>67</v>
       </c>
@@ -9753,7 +10185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.25" customHeight="1">
+    <row r="15" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="117" t="s">
         <v>68</v>
       </c>
@@ -9769,7 +10201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.25" customHeight="1">
+    <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="117" t="s">
         <v>69</v>
       </c>
@@ -9785,7 +10217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="17.25" customHeight="1">
+    <row r="17" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="117" t="s">
         <v>70</v>
       </c>
@@ -9801,7 +10233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="17.25" customHeight="1">
+    <row r="18" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="117" t="s">
         <v>71</v>
       </c>
@@ -9817,7 +10249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="17.25" customHeight="1">
+    <row r="19" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="117" t="s">
         <v>72</v>
       </c>
@@ -9833,7 +10265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="17.25" customHeight="1">
+    <row r="20" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="117" t="s">
         <v>73</v>
       </c>
@@ -9849,7 +10281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="17.25" customHeight="1">
+    <row r="21" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="117" t="s">
         <v>74</v>
       </c>
@@ -9865,7 +10297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17.25" customHeight="1">
+    <row r="22" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="117" t="s">
         <v>76</v>
       </c>
@@ -9881,7 +10313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="17.25" customHeight="1">
+    <row r="23" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="117" t="s">
         <v>77</v>
       </c>
@@ -9897,7 +10329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="17.25" customHeight="1">
+    <row r="24" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="117" t="s">
         <v>78</v>
       </c>
@@ -9914,7 +10346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="17.25" customHeight="1">
+    <row r="25" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="117" t="s">
         <v>79</v>
       </c>
@@ -9930,7 +10362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="17.25" customHeight="1">
+    <row r="26" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="117" t="s">
         <v>81</v>
       </c>
@@ -9946,7 +10378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="17.25" customHeight="1">
+    <row r="27" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="117" t="s">
         <v>82</v>
       </c>
@@ -9962,7 +10394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="17.25" customHeight="1">
+    <row r="28" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="117" t="s">
         <v>83</v>
       </c>
@@ -9979,7 +10411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="17.25" customHeight="1">
+    <row r="29" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="117" t="s">
         <v>84</v>
       </c>
@@ -9995,7 +10427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="17.25" customHeight="1">
+    <row r="30" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="117" t="s">
         <v>85</v>
       </c>
@@ -10011,7 +10443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="17.25" customHeight="1">
+    <row r="31" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="117" t="s">
         <v>86</v>
       </c>
@@ -10027,7 +10459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="17.25" customHeight="1">
+    <row r="32" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="117" t="s">
         <v>87</v>
       </c>
@@ -10043,7 +10475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="17.25" customHeight="1">
+    <row r="33" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="117" t="s">
         <v>88</v>
       </c>
@@ -10059,7 +10491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="17.25" customHeight="1">
+    <row r="34" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="117" t="s">
         <v>89</v>
       </c>
@@ -10075,7 +10507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="17.25" customHeight="1">
+    <row r="35" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="117" t="s">
         <v>90</v>
       </c>
@@ -10091,7 +10523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="17.25" customHeight="1">
+    <row r="36" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="117" t="s">
         <v>91</v>
       </c>
@@ -10107,7 +10539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="17.25" customHeight="1">
+    <row r="37" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="117" t="s">
         <v>92</v>
       </c>
@@ -10123,7 +10555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="17.25" customHeight="1">
+    <row r="38" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="117" t="s">
         <v>93</v>
       </c>
@@ -10140,7 +10572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="17.25" customHeight="1">
+    <row r="39" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="117" t="s">
         <v>94</v>
       </c>
@@ -10156,7 +10588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="17.25" customHeight="1">
+    <row r="40" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="117" t="s">
         <v>95</v>
       </c>
@@ -10172,7 +10604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="17.25" customHeight="1">
+    <row r="41" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="117" t="s">
         <v>96</v>
       </c>
@@ -10188,7 +10620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="17.25" customHeight="1">
+    <row r="42" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="117" t="s">
         <v>97</v>
       </c>
@@ -10204,7 +10636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="17.25" customHeight="1">
+    <row r="43" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="117" t="s">
         <v>98</v>
       </c>
@@ -10220,7 +10652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="17.25" customHeight="1">
+    <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="117" t="s">
         <v>99</v>
       </c>
@@ -10236,7 +10668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="17.25" customHeight="1">
+    <row r="45" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="117" t="s">
         <v>100</v>
       </c>
@@ -10252,7 +10684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="17.25" customHeight="1">
+    <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="117" t="s">
         <v>101</v>
       </c>
@@ -10268,7 +10700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="17.25" customHeight="1">
+    <row r="47" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="117" t="s">
         <v>102</v>
       </c>
@@ -10284,7 +10716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="17.25" customHeight="1">
+    <row r="48" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="117" t="s">
         <v>103</v>
       </c>
@@ -10300,7 +10732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="17.25" customHeight="1">
+    <row r="49" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="117" t="s">
         <v>104</v>
       </c>
@@ -10316,7 +10748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="17.25" customHeight="1">
+    <row r="50" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="117" t="s">
         <v>105</v>
       </c>
@@ -10333,7 +10765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="17.25" customHeight="1">
+    <row r="51" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="117" t="s">
         <v>106</v>
       </c>
@@ -10350,7 +10782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="17.25" customHeight="1">
+    <row r="52" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="117" t="s">
         <v>107</v>
       </c>
@@ -10366,7 +10798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="17.25" customHeight="1">
+    <row r="53" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="117" t="s">
         <v>108</v>
       </c>
@@ -10382,7 +10814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="17.25" customHeight="1">
+    <row r="54" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="117" t="s">
         <v>109</v>
       </c>
@@ -10398,7 +10830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="17.25" customHeight="1">
+    <row r="55" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="117" t="s">
         <v>110</v>
       </c>
@@ -10414,7 +10846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="17.25" customHeight="1">
+    <row r="56" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="117" t="s">
         <v>111</v>
       </c>
@@ -10430,7 +10862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="17.25" customHeight="1">
+    <row r="57" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="117" t="s">
         <v>112</v>
       </c>
@@ -10446,7 +10878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="17.25" customHeight="1">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="117" t="s">
         <v>113</v>
       </c>
@@ -10462,7 +10894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="17.25" customHeight="1">
+    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="117" t="s">
         <v>114</v>
       </c>
@@ -10478,7 +10910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="17.25" customHeight="1">
+    <row r="60" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="117" t="s">
         <v>115</v>
       </c>
@@ -10494,7 +10926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="17.25" customHeight="1">
+    <row r="61" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="117" t="s">
         <v>116</v>
       </c>
@@ -10510,7 +10942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="17.25" customHeight="1">
+    <row r="62" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="117" t="s">
         <v>117</v>
       </c>
@@ -10526,7 +10958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="17.25" customHeight="1">
+    <row r="63" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="117" t="s">
         <v>118</v>
       </c>
@@ -10542,7 +10974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="17.25" customHeight="1">
+    <row r="64" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="117" t="s">
         <v>119</v>
       </c>
@@ -10558,7 +10990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="17.25" customHeight="1">
+    <row r="65" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="117" t="s">
         <v>120</v>
       </c>
@@ -10574,7 +11006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="17.25" customHeight="1">
+    <row r="66" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="117" t="s">
         <v>121</v>
       </c>
@@ -10590,7 +11022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="17.25" customHeight="1">
+    <row r="67" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="117" t="s">
         <v>122</v>
       </c>
@@ -10606,7 +11038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="17.25" customHeight="1">
+    <row r="68" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="117" t="s">
         <v>123</v>
       </c>
@@ -10622,7 +11054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="17.25" customHeight="1">
+    <row r="69" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="117" t="s">
         <v>125</v>
       </c>
@@ -10638,7 +11070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="17.25" customHeight="1">
+    <row r="70" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="117" t="s">
         <v>127</v>
       </c>
@@ -10654,7 +11086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="17.25" customHeight="1">
+    <row r="71" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="117" t="s">
         <v>129</v>
       </c>
@@ -10670,7 +11102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="17.25" customHeight="1">
+    <row r="72" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="117" t="s">
         <v>130</v>
       </c>
@@ -10686,7 +11118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="17.25" customHeight="1">
+    <row r="73" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="117" t="s">
         <v>131</v>
       </c>
@@ -10702,7 +11134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="17.25" customHeight="1">
+    <row r="74" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="117" t="s">
         <v>132</v>
       </c>
@@ -10718,7 +11150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="17.25" customHeight="1">
+    <row r="75" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="117" t="s">
         <v>133</v>
       </c>
@@ -10734,7 +11166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="17.25" customHeight="1">
+    <row r="76" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="117" t="s">
         <v>134</v>
       </c>
@@ -10750,7 +11182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="17.25" customHeight="1">
+    <row r="77" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="117" t="s">
         <v>135</v>
       </c>
@@ -10766,7 +11198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="17.25" customHeight="1">
+    <row r="78" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="117" t="s">
         <v>136</v>
       </c>
@@ -10782,7 +11214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="17.25" customHeight="1">
+    <row r="79" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="117" t="s">
         <v>137</v>
       </c>
@@ -10798,7 +11230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="17.25" customHeight="1">
+    <row r="80" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="117" t="s">
         <v>138</v>
       </c>
@@ -10814,7 +11246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="17.25" customHeight="1">
+    <row r="81" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="117" t="s">
         <v>139</v>
       </c>
@@ -10830,7 +11262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="17.25" customHeight="1">
+    <row r="82" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="117" t="s">
         <v>141</v>
       </c>
@@ -10846,7 +11278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="17.25" customHeight="1">
+    <row r="83" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="117" t="s">
         <v>142</v>
       </c>
@@ -10862,7 +11294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="17.25" customHeight="1">
+    <row r="84" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="117" t="s">
         <v>143</v>
       </c>
@@ -10878,7 +11310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="17.25" customHeight="1">
+    <row r="85" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="117" t="s">
         <v>144</v>
       </c>
@@ -10894,7 +11326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="17.25" customHeight="1">
+    <row r="86" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="117" t="s">
         <v>146</v>
       </c>
@@ -10910,7 +11342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="17.25" customHeight="1">
+    <row r="87" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="117" t="s">
         <v>147</v>
       </c>
@@ -10926,7 +11358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="17.25" customHeight="1">
+    <row r="88" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="117" t="s">
         <v>148</v>
       </c>
@@ -10942,7 +11374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="17.25" customHeight="1">
+    <row r="89" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="117" t="s">
         <v>149</v>
       </c>
@@ -10958,7 +11390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="17.25" customHeight="1">
+    <row r="90" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="117" t="s">
         <v>150</v>
       </c>
@@ -10974,7 +11406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="17.25" customHeight="1">
+    <row r="91" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="117" t="s">
         <v>151</v>
       </c>
@@ -10990,7 +11422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="17.25" customHeight="1">
+    <row r="92" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="117" t="s">
         <v>152</v>
       </c>
@@ -11006,7 +11438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="17.25" customHeight="1">
+    <row r="93" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="117" t="s">
         <v>153</v>
       </c>
@@ -11022,7 +11454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="17.25" customHeight="1">
+    <row r="94" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="117" t="s">
         <v>154</v>
       </c>
@@ -11038,7 +11470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="17.25" customHeight="1">
+    <row r="95" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="117" t="s">
         <v>155</v>
       </c>
@@ -11054,7 +11486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="17.25" customHeight="1">
+    <row r="96" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="117" t="s">
         <v>156</v>
       </c>
@@ -11070,7 +11502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="17.25" customHeight="1">
+    <row r="97" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="117" t="s">
         <v>157</v>
       </c>
@@ -11086,7 +11518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="17.25" customHeight="1">
+    <row r="98" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="117" t="s">
         <v>158</v>
       </c>
@@ -11102,7 +11534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="17.25" customHeight="1">
+    <row r="99" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="117" t="s">
         <v>159</v>
       </c>
@@ -11118,20 +11550,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="17.25" customHeight="1">
+    <row r="100" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="117" t="s">
         <v>160</v>
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>46076.541597106479</v>
+        <v>46288.356350231479</v>
       </c>
       <c r="D100" s="117">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="17.25" customHeight="1">
+    <row r="101" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="117" t="s">
         <v>161</v>
       </c>
@@ -11147,7 +11579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="17.25" customHeight="1">
+    <row r="102" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="117" t="s">
         <v>162</v>
       </c>
@@ -11163,7 +11595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="17.25" customHeight="1">
+    <row r="103" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="117" t="s">
         <v>163</v>
       </c>
@@ -11179,7 +11611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="17.25" customHeight="1">
+    <row r="104" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="117" t="s">
         <v>164</v>
       </c>
@@ -11195,7 +11627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="17.25" customHeight="1">
+    <row r="105" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="117" t="s">
         <v>165</v>
       </c>
@@ -11211,7 +11643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="17.25" customHeight="1">
+    <row r="106" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="117" t="s">
         <v>166</v>
       </c>
@@ -11227,7 +11659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="17.25" customHeight="1">
+    <row r="107" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="117" t="s">
         <v>167</v>
       </c>
@@ -11243,7 +11675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="17.25" customHeight="1">
+    <row r="108" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="117" t="s">
         <v>168</v>
       </c>
@@ -11259,7 +11691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="17.25" customHeight="1">
+    <row r="109" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="117" t="s">
         <v>169</v>
       </c>
@@ -11275,7 +11707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="17.25" customHeight="1">
+    <row r="110" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="117" t="s">
         <v>170</v>
       </c>
@@ -11291,7 +11723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="17.25" customHeight="1">
+    <row r="111" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="117" t="s">
         <v>171</v>
       </c>
@@ -11307,12 +11739,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="17.25" customHeight="1">
+    <row r="112" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="117"/>
       <c r="B112" s="117"/>
       <c r="D112" s="117"/>
     </row>
-    <row r="113" spans="1:4" ht="17.25" customHeight="1">
+    <row r="113" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="117" t="s">
         <v>172</v>
       </c>
@@ -11328,7 +11760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="17.25" customHeight="1">
+    <row r="114" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="117" t="s">
         <v>173</v>
       </c>
@@ -11344,7 +11776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="17.25" customHeight="1">
+    <row r="115" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="117" t="s">
         <v>175</v>
       </c>
@@ -11360,7 +11792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="17.25" customHeight="1">
+    <row r="116" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="117" t="s">
         <v>177</v>
       </c>
@@ -11376,7 +11808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="17.25" customHeight="1">
+    <row r="117" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="117" t="s">
         <v>178</v>
       </c>
@@ -11392,7 +11824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="17.25" customHeight="1">
+    <row r="118" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="117" t="s">
         <v>179</v>
       </c>
@@ -11408,7 +11840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="17.25" customHeight="1">
+    <row r="119" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="117" t="s">
         <v>180</v>
       </c>
@@ -11424,7 +11856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="17.25" customHeight="1">
+    <row r="120" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="117" t="s">
         <v>181</v>
       </c>
@@ -11440,7 +11872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="17.25" customHeight="1">
+    <row r="121" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="117" t="s">
         <v>182</v>
       </c>
@@ -11456,7 +11888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="17.25" customHeight="1">
+    <row r="122" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="117" t="s">
         <v>183</v>
       </c>
@@ -11472,7 +11904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="17.25" customHeight="1">
+    <row r="123" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="117" t="s">
         <v>184</v>
       </c>
@@ -11488,7 +11920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="17.25" customHeight="1">
+    <row r="124" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="117" t="s">
         <v>185</v>
       </c>
@@ -11504,7 +11936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="17.25" customHeight="1">
+    <row r="125" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="117" t="s">
         <v>186</v>
       </c>
@@ -11520,7 +11952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="17.25" customHeight="1">
+    <row r="126" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="117" t="s">
         <v>187</v>
       </c>
@@ -11536,7 +11968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="17.25" customHeight="1">
+    <row r="127" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="117" t="s">
         <v>188</v>
       </c>
@@ -11552,7 +11984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="17.25" customHeight="1">
+    <row r="128" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="117" t="s">
         <v>189</v>
       </c>
@@ -11568,7 +12000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="17.25" customHeight="1">
+    <row r="129" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="117" t="s">
         <v>190</v>
       </c>
@@ -11584,7 +12016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="17.25" customHeight="1">
+    <row r="130" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="117" t="s">
         <v>191</v>
       </c>
@@ -11600,7 +12032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="17.25" customHeight="1">
+    <row r="131" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="117" t="s">
         <v>192</v>
       </c>
@@ -11616,7 +12048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="17.25" customHeight="1">
+    <row r="132" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="117" t="s">
         <v>193</v>
       </c>
@@ -11632,7 +12064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="17.25" customHeight="1">
+    <row r="133" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="117" t="s">
         <v>194</v>
       </c>
@@ -11648,7 +12080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="17.25" customHeight="1">
+    <row r="134" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="117" t="s">
         <v>195</v>
       </c>
@@ -11664,7 +12096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="17.25" customHeight="1">
+    <row r="135" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="117" t="s">
         <v>196</v>
       </c>
@@ -11680,7 +12112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="17.25" customHeight="1">
+    <row r="136" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="117" t="s">
         <v>198</v>
       </c>
@@ -11696,7 +12128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="17.25" customHeight="1">
+    <row r="137" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="117" t="s">
         <v>199</v>
       </c>
@@ -11712,7 +12144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="17.25" customHeight="1">
+    <row r="138" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="117" t="s">
         <v>200</v>
       </c>
@@ -11728,7 +12160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="17.25" customHeight="1">
+    <row r="139" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="117" t="s">
         <v>201</v>
       </c>
@@ -11744,7 +12176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="17.25" customHeight="1">
+    <row r="140" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="117" t="s">
         <v>202</v>
       </c>
@@ -11760,7 +12192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="17.25" customHeight="1">
+    <row r="141" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="117" t="s">
         <v>203</v>
       </c>
@@ -11776,7 +12208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="17.25" customHeight="1">
+    <row r="142" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="117" t="s">
         <v>205</v>
       </c>
@@ -11792,7 +12224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="17.25" customHeight="1">
+    <row r="143" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="117" t="s">
         <v>206</v>
       </c>
@@ -11808,20 +12240,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="17.25" customHeight="1">
+    <row r="144" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="117" t="s">
         <v>207</v>
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>46076</v>
+        <v>46288</v>
       </c>
       <c r="D144" s="117">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="17.25" customHeight="1">
+    <row r="145" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="117" t="s">
         <v>208</v>
       </c>
@@ -11837,7 +12269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="17.25" customHeight="1">
+    <row r="146" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="117" t="s">
         <v>210</v>
       </c>
@@ -11853,7 +12285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="17.25" customHeight="1">
+    <row r="147" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="117" t="s">
         <v>211</v>
       </c>
@@ -11869,7 +12301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="17.25" customHeight="1">
+    <row r="148" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="117" t="s">
         <v>213</v>
       </c>
@@ -11885,7 +12317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="17.25" customHeight="1">
+    <row r="149" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="117" t="s">
         <v>214</v>
       </c>
@@ -11901,7 +12333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="17.25" customHeight="1">
+    <row r="150" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="117" t="s">
         <v>215</v>
       </c>
@@ -11917,7 +12349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="17.25" customHeight="1">
+    <row r="151" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="117" t="s">
         <v>216</v>
       </c>
@@ -11933,7 +12365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="17.25" customHeight="1">
+    <row r="152" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="117" t="s">
         <v>217</v>
       </c>
@@ -11949,7 +12381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="17.25" customHeight="1">
+    <row r="153" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="117" t="s">
         <v>218</v>
       </c>
@@ -11965,7 +12397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="17.25" customHeight="1">
+    <row r="154" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="117" t="s">
         <v>219</v>
       </c>
@@ -11982,7 +12414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="17.25" customHeight="1">
+    <row r="155" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="117" t="s">
         <v>220</v>
       </c>
@@ -11998,7 +12430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="17.25" customHeight="1">
+    <row r="156" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="117" t="s">
         <v>221</v>
       </c>
@@ -12014,7 +12446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="17.25" customHeight="1">
+    <row r="157" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="117" t="s">
         <v>222</v>
       </c>
@@ -12030,7 +12462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="17.25" customHeight="1">
+    <row r="158" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="117" t="s">
         <v>223</v>
       </c>
@@ -12046,7 +12478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="17.25" customHeight="1">
+    <row r="159" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="117" t="s">
         <v>224</v>
       </c>
@@ -12062,7 +12494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="17.25" customHeight="1">
+    <row r="160" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="117" t="s">
         <v>225</v>
       </c>
@@ -12078,7 +12510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="17.25" customHeight="1">
+    <row r="161" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="117" t="s">
         <v>226</v>
       </c>
@@ -12094,7 +12526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="17.25" customHeight="1">
+    <row r="162" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="117" t="s">
         <v>227</v>
       </c>
@@ -12110,7 +12542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="17.25" customHeight="1">
+    <row r="163" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="117" t="s">
         <v>229</v>
       </c>
@@ -12128,10 +12560,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D180">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12145,8 +12577,8 @@
     <tabColor rgb="FFFF0000"/>
     <outlinePr summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:R30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="A1:R31"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
@@ -12156,17 +12588,17 @@
     <col min="15" max="18" width="9.140625" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>230</v>
       </c>
       <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="122" t="s">
+      <c r="D1" s="123" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="122"/>
+      <c r="E1" s="123"/>
       <c r="F1" t="s">
         <v>233</v>
       </c>
@@ -12174,19 +12606,19 @@
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="122"/>
-      <c r="E2" s="122"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
       <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D3" s="85" t="s">
         <v>235</v>
       </c>
@@ -12194,29 +12626,43 @@
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="75" customHeight="1">
+    <row r="5" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:8" outlineLevel="1"/>
-    <row r="11" spans="1:8" outlineLevel="1"/>
-    <row r="12" spans="1:8" hidden="1" outlineLevel="2"/>
-    <row r="13" spans="1:8" hidden="1" outlineLevel="2"/>
-    <row r="14" spans="1:8" hidden="1" outlineLevel="2"/>
-    <row r="15" spans="1:8" outlineLevel="1" collapsed="1"/>
-    <row r="16" spans="1:8" outlineLevel="1"/>
-    <row r="17" spans="1:1" outlineLevel="1"/>
-    <row r="18" spans="1:1" outlineLevel="1"/>
-    <row r="30" spans="1:1">
-      <c r="A30" t="e" cm="1">
-        <f t="array" aca="1" ref="A30" ca="1">RANDARRAY(2, 2)</f>
-        <v>#NAME?</v>
+    <row r="10" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:8" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="1:2" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:2" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" cm="1">
+        <f t="array" aca="1" ref="A30:B31" ca="1">_xlfn.RANDARRAY(2, 2)</f>
+        <v>0.81032257102058525</v>
+      </c>
+      <c r="B30">
+        <f ca="1"/>
+        <v>0.28311289973983134</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <f ca="1"/>
+        <v>0.40396537523061316</v>
+      </c>
+      <c r="B31">
+        <f ca="1"/>
+        <v>0.11664411871859959</v>
       </c>
     </row>
   </sheetData>
@@ -12235,14 +12681,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF68F2C0-1053-4FB6-BD74-8A11B0CAF123}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="13.5" thickBot="1">
+    <row r="1" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="68" t="s">
         <v>239</v>
       </c>
@@ -12264,7 +12710,7 @@
       </c>
       <c r="M1" s="36"/>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="40" t="s">
         <v>245</v>
       </c>
@@ -12290,7 +12736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="41" t="s">
         <v>252</v>
       </c>
@@ -12313,7 +12759,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15">
+    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="42" t="s">
         <v>256</v>
       </c>
@@ -12339,7 +12785,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
         <v>262</v>
       </c>
@@ -12359,7 +12805,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="44" t="s">
         <v>266</v>
       </c>
@@ -12382,7 +12828,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75">
+    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="45" t="s">
         <v>271</v>
       </c>
@@ -12402,7 +12848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21">
+    <row r="8" spans="1:13" ht="21" x14ac:dyDescent="0.35">
       <c r="A8" s="46" t="s">
         <v>275</v>
       </c>
@@ -12425,7 +12871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="47" t="s">
         <v>280</v>
       </c>
@@ -12442,7 +12888,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="48" t="s">
         <v>283</v>
       </c>
@@ -12450,7 +12896,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="13.5" thickBot="1">
+    <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="49" t="s">
         <v>285</v>
       </c>
@@ -12459,7 +12905,7 @@
       </c>
       <c r="F11" s="36"/>
     </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1">
+    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="50" t="s">
         <v>287</v>
       </c>
@@ -12473,7 +12919,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="51" t="s">
         <v>290</v>
       </c>
@@ -12484,7 +12930,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="52" t="s">
         <v>291</v>
       </c>
@@ -12498,7 +12944,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1">
+    <row r="15" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="53" t="s">
         <v>293</v>
       </c>
@@ -12509,7 +12955,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
+    <row r="16" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="54" t="s">
         <v>294</v>
       </c>
@@ -12523,12 +12969,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="13.5" thickBot="1">
+    <row r="17" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="55" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="13.5" thickBot="1">
+    <row r="18" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="74" t="s">
         <v>297</v>
       </c>
@@ -12540,7 +12986,7 @@
       </c>
       <c r="F18" s="36"/>
     </row>
-    <row r="19" spans="1:6" ht="13.5" thickBot="1">
+    <row r="19" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="75" t="s">
         <v>300</v>
       </c>
@@ -12551,7 +12997,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="51.75" thickBot="1">
+    <row r="20" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="76" t="s">
         <v>303</v>
       </c>
@@ -12565,12 +13011,12 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="13.5" thickBot="1">
+    <row r="21" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="77" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="13.5" thickBot="1">
+    <row r="22" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="78" t="s">
         <v>307</v>
       </c>
@@ -12579,13 +13025,13 @@
       </c>
       <c r="E22" s="21"/>
     </row>
-    <row r="23" spans="1:6" ht="13.5" thickBot="1">
+    <row r="23" spans="1:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="79" t="s">
         <v>309</v>
       </c>
       <c r="E23" s="21"/>
     </row>
-    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
+    <row r="24" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="80" t="s">
         <v>310</v>
       </c>
@@ -12594,20 +13040,20 @@
       </c>
       <c r="E24" s="21"/>
     </row>
-    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
-    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
+    <row r="25" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C26" s="67" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1"/>
-    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1">
+    <row r="27" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:6" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C28" s="88" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="13.5" thickTop="1"/>
-    <row r="30" spans="1:6">
+    <row r="29" spans="1:6" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C30" s="87" t="s">
         <v>314</v>
       </c>
@@ -12621,13 +13067,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D919E811-4385-4D35-A19E-3B7E0E659A89}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.5" thickBot="1">
+    <row r="1" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
         <v>315</v>
       </c>
@@ -12644,7 +13090,7 @@
       <c r="I1" s="36"/>
       <c r="J1" s="36"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="38" t="s">
         <v>319</v>
       </c>
@@ -12667,7 +13113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="38" t="s">
         <v>321</v>
       </c>
@@ -12690,7 +13136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="38" t="s">
         <v>325</v>
       </c>
@@ -12710,7 +13156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
         <v>328</v>
       </c>
@@ -12734,7 +13180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
         <v>330</v>
       </c>
@@ -12757,7 +13203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="38" t="s">
         <v>333</v>
       </c>
@@ -12783,7 +13229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
         <v>337</v>
       </c>
@@ -12794,7 +13240,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="38" t="s">
         <v>339</v>
       </c>
@@ -12803,7 +13249,7 @@
       </c>
       <c r="C9" s="21"/>
     </row>
-    <row r="10" spans="1:10" ht="13.5" thickBot="1">
+    <row r="10" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="38" t="s">
         <v>340</v>
       </c>
@@ -12821,7 +13267,7 @@
       <c r="I10" s="36"/>
       <c r="J10" s="36"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="38" t="s">
         <v>342</v>
       </c>
@@ -12844,13 +13290,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="38" t="s">
         <v>344</v>
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>46076</v>
+        <v>46288</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
@@ -12869,7 +13315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="38" t="s">
         <v>346</v>
       </c>
@@ -12892,7 +13338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="38" t="s">
         <v>348</v>
       </c>
@@ -12918,7 +13364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="38" t="s">
         <v>350</v>
       </c>
@@ -12938,7 +13384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="38" t="s">
         <v>352</v>
       </c>
@@ -12961,7 +13407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="38" t="s">
         <v>354</v>
       </c>
@@ -12984,7 +13430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="38" t="s">
         <v>356</v>
       </c>
@@ -13007,7 +13453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="38" t="s">
         <v>358</v>
       </c>
@@ -13030,7 +13476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="38" t="s">
         <v>360</v>
       </c>
@@ -13053,7 +13499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="38" t="s">
         <v>362</v>
       </c>
@@ -13079,7 +13525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="38" t="s">
         <v>364</v>
       </c>
@@ -13105,7 +13551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="38" t="s">
         <v>366</v>
       </c>
@@ -13131,7 +13577,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G24" s="34" t="s">
         <v>368</v>
       </c>
@@ -13148,7 +13594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="38" t="s">
         <v>369</v>
       </c>
@@ -13174,7 +13620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G26" s="34" t="s">
         <v>371</v>
       </c>
@@ -13194,7 +13640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="21" t="s">
         <v>372</v>
       </c>
@@ -13220,7 +13666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G28" s="34" t="s">
         <v>374</v>
       </c>
@@ -13240,7 +13686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="38" t="s">
         <v>375</v>
       </c>
@@ -13269,7 +13715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G30" s="34" t="s">
         <v>377</v>
       </c>
@@ -13289,7 +13735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="13.5" thickBot="1">
+    <row r="31" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G31" s="35" t="s">
         <v>378</v>
       </c>
@@ -13303,7 +13749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G32" s="34" t="s">
         <v>379</v>
       </c>
@@ -13317,7 +13763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="7:10">
+    <row r="33" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G33" s="34" t="s">
         <v>380</v>
       </c>
@@ -13331,7 +13777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="7:10">
+    <row r="34" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G34" s="34" t="s">
         <v>381</v>
       </c>
@@ -13345,7 +13791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="7:10">
+    <row r="35" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G35" s="34" t="s">
         <v>382</v>
       </c>
@@ -13359,7 +13805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="7:10">
+    <row r="36" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G36" s="34" t="s">
         <v>383</v>
       </c>
@@ -13373,7 +13819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="7:10">
+    <row r="37" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G37" s="34" t="s">
         <v>384</v>
       </c>
@@ -13387,110 +13833,110 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="7:10">
+    <row r="39" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G39" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="B15">
-    <cfRule type="expression" dxfId="41" priority="59">
+    <cfRule type="expression" dxfId="23" priority="59">
       <formula>ODD(B15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="cellIs" dxfId="40" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="47" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2">
-    <cfRule type="aboveAverage" dxfId="39" priority="115"/>
+    <cfRule type="aboveAverage" dxfId="21" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="beginsWith" dxfId="38" priority="74" operator="beginsWith" text="rule">
+    <cfRule type="beginsWith" dxfId="20" priority="74" operator="beginsWith" text="rule">
       <formula>LEFT(B3,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="containsBlanks" dxfId="37" priority="72">
+    <cfRule type="containsBlanks" dxfId="19" priority="72">
       <formula>LEN(TRIM(B4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:C5">
-    <cfRule type="containsErrors" dxfId="36" priority="71">
+    <cfRule type="containsErrors" dxfId="18" priority="71">
       <formula>ISERROR(B5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="containsText" dxfId="35" priority="70" operator="containsText" text="rule">
+    <cfRule type="containsText" dxfId="17" priority="70" operator="containsText" text="rule">
       <formula>NOT(ISERROR(SEARCH("rule",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:C8">
-    <cfRule type="endsWith" dxfId="34" priority="68" operator="endsWith" text="rule">
+    <cfRule type="endsWith" dxfId="16" priority="68" operator="endsWith" text="rule">
       <formula>RIGHT(B8,LEN("rule"))="rule"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="notContainsBlanks" dxfId="33" priority="67">
+    <cfRule type="notContainsBlanks" dxfId="15" priority="67">
       <formula>LEN(TRIM(B9))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:C10">
-    <cfRule type="notContainsErrors" dxfId="32" priority="66">
+    <cfRule type="notContainsErrors" dxfId="14" priority="66">
       <formula>NOT(ISERROR(B10))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:C11">
-    <cfRule type="notContainsText" dxfId="31" priority="65" operator="notContains" text="rule">
+    <cfRule type="notContainsText" dxfId="13" priority="65" operator="notContains" text="rule">
       <formula>ISERROR(SEARCH("rule",B11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:C12">
-    <cfRule type="timePeriod" dxfId="30" priority="64" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="12" priority="64" timePeriod="today">
       <formula>FLOOR(B12,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:C13">
-    <cfRule type="top10" dxfId="29" priority="116" rank="1"/>
+    <cfRule type="top10" dxfId="11" priority="116" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:C16">
-    <cfRule type="cellIs" dxfId="28" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="46" operator="equal">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:C17">
-    <cfRule type="cellIs" dxfId="27" priority="57" operator="notEqual">
+    <cfRule type="cellIs" dxfId="9" priority="57" operator="notEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:C18">
-    <cfRule type="cellIs" dxfId="26" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:C20">
-    <cfRule type="cellIs" dxfId="24" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:C21">
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22">
-    <cfRule type="cellIs" dxfId="22" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="between">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="notBetween">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="notBetween">
       <formula>2</formula>
       <formula>4</formula>
     </cfRule>
@@ -13524,16 +13970,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29:C29">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="between">
       <formula>$B$23</formula>
       <formula>2+2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D7">
-    <cfRule type="duplicateValues" dxfId="19" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D14">
-    <cfRule type="uniqueValues" dxfId="18" priority="97"/>
+    <cfRule type="uniqueValues" dxfId="0" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:J2">
     <cfRule type="colorScale" priority="45">
@@ -13956,7 +14402,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CCC4B1-5C65-4837-AA26-56CCF06B63BB}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" customWidth="1"/>
@@ -13968,12 +14414,12 @@
     <col min="10" max="10" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15">
+    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="C3" s="17" t="s">
         <v>35</v>
       </c>
@@ -13999,7 +14445,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C4" s="117" t="s">
         <v>42</v>
       </c>
@@ -14030,7 +14476,7 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C5" s="117" t="s">
         <v>44</v>
       </c>
@@ -14061,7 +14507,7 @@
         <v>Rank</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C6" s="117" t="s">
         <v>392</v>
       </c>
@@ -14094,7 +14540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>393</v>
       </c>
@@ -14120,7 +14566,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C9">
         <v>3</v>
       </c>
@@ -14148,7 +14594,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>399</v>
       </c>
@@ -14159,7 +14605,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C12">
         <v>3</v>
       </c>
@@ -14167,7 +14613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>402</v>
       </c>
@@ -14178,7 +14624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C15">
         <v>3</v>
       </c>
@@ -14186,7 +14632,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>403</v>
       </c>
@@ -14197,7 +14643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C18">
         <v>3</v>
       </c>
@@ -14205,7 +14651,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>404</v>
       </c>
@@ -14216,7 +14662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:4">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C21">
         <v>3</v>
       </c>
@@ -14224,7 +14670,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>405</v>
       </c>
@@ -14235,7 +14681,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:4">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C24">
         <v>3</v>
       </c>
@@ -14243,7 +14689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:4">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>406</v>
       </c>
@@ -14254,7 +14700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:4">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C27">
         <v>3</v>
       </c>
@@ -14262,7 +14708,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="2:4">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C28" t="s">
         <v>392</v>
       </c>
@@ -14271,7 +14717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="2:4">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>407</v>
       </c>
@@ -14282,7 +14728,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="31" spans="2:4" hidden="1">
+    <row r="31" spans="2:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="C31" t="s">
         <v>410</v>
       </c>
@@ -14290,7 +14736,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="32" spans="2:4">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C32" t="s">
         <v>411</v>
       </c>
@@ -14298,7 +14744,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>412</v>
       </c>
@@ -14323,7 +14769,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9224F2-4D06-4586-886C-E51F5EBCA7B0}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -14344,7 +14790,7 @@
     <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15">
+    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="92" t="s">
         <v>413</v>
       </c>
@@ -14354,7 +14800,7 @@
       <c r="E1" s="17"/>
       <c r="F1" s="17"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="117"/>
       <c r="B2" s="117"/>
       <c r="C2" s="117"/>
@@ -14362,7 +14808,7 @@
       <c r="E2" s="117"/>
       <c r="F2" s="117"/>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="117"/>
       <c r="B3" s="117"/>
       <c r="C3" s="89" t="s">
@@ -14372,7 +14818,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="117"/>
       <c r="B4" s="117"/>
       <c r="C4" s="89" t="s">
@@ -14406,7 +14852,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="117"/>
       <c r="B5" s="117"/>
       <c r="C5" s="90" t="s">
@@ -14419,7 +14865,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="117"/>
       <c r="B6" s="117"/>
       <c r="C6" s="91">
@@ -14432,7 +14878,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="117"/>
       <c r="B7" s="117"/>
       <c r="C7" s="90" t="s">
@@ -14445,7 +14891,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="117"/>
       <c r="B8" s="117"/>
       <c r="C8" s="91">
@@ -14458,7 +14904,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="117"/>
       <c r="B9" s="117"/>
       <c r="C9" s="90" t="s">
@@ -14471,7 +14917,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="117"/>
       <c r="B10" s="117"/>
       <c r="C10" s="91">
@@ -14484,7 +14930,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="90" t="s">
         <v>44</v>
       </c>
@@ -14495,7 +14941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="91">
         <v>23000</v>
       </c>
@@ -14506,7 +14952,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="90" t="s">
         <v>50</v>
       </c>
@@ -14517,7 +14963,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="91">
         <v>2</v>
       </c>
@@ -14528,7 +14974,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="90" t="s">
         <v>48</v>
       </c>
@@ -14539,7 +14985,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C16" s="91">
         <v>50024</v>
       </c>
@@ -14550,7 +14996,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="3:12">
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="90" t="s">
         <v>53</v>
       </c>
@@ -14561,7 +15007,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="3:12">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="91">
         <v>189576</v>
       </c>
@@ -14572,7 +15018,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="3:12">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="90" t="s">
         <v>57</v>
       </c>
@@ -14583,7 +15029,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="3:12">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="91">
         <v>5000</v>
       </c>
@@ -14594,7 +15040,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="3:12">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="90" t="s">
         <v>417</v>
       </c>
@@ -14635,29 +15081,29 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C47BF70-BA80-4124-B359-67CBCB635390}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="65.140625" customWidth="1"/>
     <col min="2" max="26" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>419</v>
       </c>
       <c r="B2" s="117"/>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>421</v>
       </c>
@@ -14671,9 +15117,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE31E21-0350-44E7-AF13-4CA140505B30}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="51">
+    <row r="1" spans="1:2" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
         <v>422</v>
       </c>
@@ -14681,7 +15127,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>408</v>
       </c>
@@ -14689,7 +15135,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -14697,7 +15143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2</v>
       </c>
@@ -14705,7 +15151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -14713,7 +15159,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>4</v>
       </c>
@@ -14721,7 +15167,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>5</v>
       </c>

--- a/tests/__xlsx__/xlsx_demo_data.xlsx
+++ b/tests/__xlsx__/xlsx_demo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Odoo\spreadsheet\tests\__xlsx__\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\odoo\spreadsheet\tests\__xlsx__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F832354-F3E9-4BC5-A260-88E8A391D52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D70715-801F-423D-A719-873B16295B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,10 +30,11 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId15"/>
+    <externalReference r:id="rId16"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId16"/>
+    <pivotCache cacheId="1" r:id="rId17"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2151,7 +2152,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2335,6 +2336,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2351,21 +2365,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2812,7 +2811,7 @@
         <u/>
         <color theme="7"/>
       </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
       <fill>
         <patternFill patternType="lightTrellis">
           <fgColor theme="4"/>
@@ -3958,6 +3957,514 @@
 </file>
 
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2200"/>
+              <a:t>chart with composite ranges</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>([2]Sheet1!$A$27:$C$35,[2]Sheet1!$A$27:$C$31)</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>24</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>27</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>45</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>17</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>43</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>11</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>16</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>24</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>27</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>45</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>48</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>45</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>25</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>31</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>20</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>19</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>16</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>48</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>45</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>25</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Emily Anderson (Emmy)</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Sophie Allen (Saffi)</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Chloe Adams</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Megan Alexander (Meg)</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Lucy Arnold (Lulu)</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Hannah Alvarez</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Jessica Alcock (Jess)</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Charlotte Anaya</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Lauren Anthony</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Emily Anderson (Emmy)</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Sophie Allen (Saffi)</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Chloe Adams</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Megan Alexander (Meg)</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Lucy Arnold (Lulu)</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[2]Sheet1!$B$27:$B$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="7030A0"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A1E9-46C7-8442-4AB5744608FB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C65911"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="C65911"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>[2]Sheet1!$A$27:$A$31</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Emily Anderson (Emmy)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sophie Allen (Saffi)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chloe Adams</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Megan Alexander (Meg)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Lucy Arnold (Lulu)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[2]Sheet1!$C$27:$C$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="C65911"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A1E9-46C7-8442-4AB5744608FB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="70"/>
+        <c:overlap val="-20"/>
+        <c:axId val="17781237"/>
+        <c:axId val="88853993"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="17781237"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="1000" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="88853993"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="88853993"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="1000" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="17781237"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr sz="1000" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln cmpd="sng">
+      <a:solidFill>
+        <a:srgbClr val="000000"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8578,6 +9085,47 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Chart 11" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F47B043-E8D8-482A-8380-D03C8E238CC3}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8702,6 +9250,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Feuil1"/>
     </sheetNames>
@@ -8713,6 +9264,149 @@
           </cell>
         </row>
       </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Formulas"/>
+      <sheetName val="jestSheet"/>
+      <sheetName val="jestStyles"/>
+      <sheetName val="jestCfs"/>
+      <sheetName val="jestTable"/>
+      <sheetName val="jestPivot"/>
+      <sheetName val="jestCharts"/>
+      <sheetName val="jestMiscTest"/>
+      <sheetName val="jestHiddenSheet"/>
+      <sheetName val="jestFreezePane"/>
+      <sheetName val="jestImages"/>
+      <sheetName val="jestOneCellAnchor"/>
+      <sheetName val="jestDataValidations"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="27">
+          <cell r="A27" t="str">
+            <v>Emily Anderson (Emmy)</v>
+          </cell>
+          <cell r="B27">
+            <v>12</v>
+          </cell>
+          <cell r="C27">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28" t="str">
+            <v>Sophie Allen (Saffi)</v>
+          </cell>
+          <cell r="B28">
+            <v>48</v>
+          </cell>
+          <cell r="C28">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29" t="str">
+            <v>Chloe Adams</v>
+          </cell>
+          <cell r="B29">
+            <v>45</v>
+          </cell>
+          <cell r="C29">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>Megan Alexander (Meg)</v>
+          </cell>
+          <cell r="B30">
+            <v>1</v>
+          </cell>
+          <cell r="C30">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31" t="str">
+            <v>Lucy Arnold (Lulu)</v>
+          </cell>
+          <cell r="B31">
+            <v>25</v>
+          </cell>
+          <cell r="C31">
+            <v>45</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32" t="str">
+            <v>Hannah Alvarez</v>
+          </cell>
+          <cell r="B32">
+            <v>31</v>
+          </cell>
+          <cell r="C32">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33" t="str">
+            <v>Jessica Alcock (Jess)</v>
+          </cell>
+          <cell r="B33">
+            <v>20</v>
+          </cell>
+          <cell r="C33">
+            <v>43</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34" t="str">
+            <v>Charlotte Anaya</v>
+          </cell>
+          <cell r="B34">
+            <v>19</v>
+          </cell>
+          <cell r="C34">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35" t="str">
+            <v>Lauren Anthony</v>
+          </cell>
+          <cell r="B35">
+            <v>16</v>
+          </cell>
+          <cell r="C35">
+            <v>16</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -8837,7 +9531,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B3CE3F5-58D8-48A3-B9C6-24D1506C9F5C}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C3:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -9463,10 +10157,10 @@
       <c r="G2" s="104">
         <v>5</v>
       </c>
-      <c r="H2" s="105" t="s">
+      <c r="H2" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="106"/>
+      <c r="I2" s="111"/>
       <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9476,10 +10170,10 @@
       <c r="G3" s="104">
         <v>8</v>
       </c>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="107">
+      <c r="K3" s="112">
         <v>5</v>
       </c>
       <c r="L3" s="6"/>
@@ -9497,10 +10191,10 @@
       <c r="G4" s="104">
         <v>9</v>
       </c>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="108"/>
+      <c r="K4" s="113"/>
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9510,10 +10204,10 @@
       <c r="G5" s="104">
         <v>15</v>
       </c>
-      <c r="H5" s="106"/>
-      <c r="I5" s="106"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="111"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="108"/>
+      <c r="K5" s="113"/>
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9521,7 +10215,7 @@
         <v>22</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="108"/>
+      <c r="K6" s="113"/>
       <c r="L6" s="6"/>
     </row>
     <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9529,7 +10223,7 @@
         <v>3</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="108"/>
+      <c r="K7" s="113"/>
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9537,7 +10231,7 @@
         <v>30</v>
       </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="109"/>
+      <c r="K8" s="114"/>
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9936,63 +10630,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="106" t="s">
         <v>423</v>
       </c>
-      <c r="B1" s="113" t="s">
+      <c r="B1" s="107" t="s">
         <v>424</v>
       </c>
-      <c r="C1" s="113" t="s">
+      <c r="C1" s="107" t="s">
         <v>425</v>
       </c>
-      <c r="D1" s="113" t="s">
+      <c r="D1" s="107" t="s">
         <v>426</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="E1" s="107" t="s">
         <v>427</v>
       </c>
-      <c r="F1" s="113" t="s">
+      <c r="F1" s="107" t="s">
         <v>428</v>
       </c>
-      <c r="G1" s="113" t="s">
+      <c r="G1" s="107" t="s">
         <v>429</v>
       </c>
-      <c r="H1" s="113" t="s">
+      <c r="H1" s="107" t="s">
         <v>430</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="108" t="s">
         <v>431</v>
       </c>
-      <c r="J1" s="111" t="s">
+      <c r="J1" s="105" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="115">
+      <c r="A2">
         <v>4</v>
       </c>
-      <c r="B2" s="115">
+      <c r="B2">
         <v>99.5</v>
       </c>
-      <c r="C2" s="115">
-        <v>1</v>
-      </c>
-      <c r="D2" s="115" t="s">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>432</v>
       </c>
-      <c r="E2" s="116">
+      <c r="E2" s="39">
         <v>45575</v>
       </c>
-      <c r="F2" s="117">
+      <c r="F2" s="109">
         <v>0.64583333333333337</v>
       </c>
-      <c r="G2" s="117" t="s">
+      <c r="G2" s="109" t="s">
         <v>433</v>
       </c>
-      <c r="H2" s="116">
+      <c r="H2" s="39">
         <v>45292</v>
       </c>
-      <c r="I2" s="115">
+      <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
@@ -10000,31 +10694,31 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="115">
+      <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3" s="115">
+      <c r="B3">
         <v>40</v>
       </c>
-      <c r="C3" s="115">
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" s="115" t="s">
+      <c r="D3" t="s">
         <v>434</v>
       </c>
-      <c r="E3" s="116">
+      <c r="E3" s="39">
         <v>45576</v>
       </c>
-      <c r="F3" s="117">
+      <c r="F3" s="109">
         <v>0.57638888888888884</v>
       </c>
-      <c r="G3" s="117" t="s">
+      <c r="G3" s="109" t="s">
         <v>435</v>
       </c>
-      <c r="H3" s="116">
+      <c r="H3" s="39">
         <v>45231</v>
       </c>
-      <c r="I3" s="115" t="s">
+      <c r="I3" t="s">
         <v>433</v>
       </c>
       <c r="J3">
@@ -10032,31 +10726,31 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="115">
+      <c r="A4">
         <v>9</v>
       </c>
-      <c r="B4" s="115">
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" s="115">
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" s="115" t="s">
+      <c r="D4" t="s">
         <v>436</v>
       </c>
-      <c r="E4" s="116">
+      <c r="E4" s="39">
         <v>45574</v>
       </c>
-      <c r="F4" s="117">
+      <c r="F4" s="109">
         <v>0.73958333333333337</v>
       </c>
-      <c r="G4" s="117" t="s">
+      <c r="G4" s="109" t="s">
         <v>437</v>
       </c>
-      <c r="H4" s="116">
+      <c r="H4" s="39">
         <v>45325</v>
       </c>
-      <c r="I4" s="115">
+      <c r="I4">
         <v>3</v>
       </c>
       <c r="J4">
@@ -10064,31 +10758,31 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="115">
+      <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5" s="115">
+      <c r="B5">
         <v>120</v>
       </c>
-      <c r="C5" s="115">
+      <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" s="115" t="s">
+      <c r="D5" t="s">
         <v>434</v>
       </c>
-      <c r="E5" s="116">
+      <c r="E5" s="39">
         <v>45573</v>
       </c>
-      <c r="F5" s="117">
+      <c r="F5" s="109">
         <v>0.66666666666666663</v>
       </c>
-      <c r="G5" s="115" t="s">
+      <c r="G5" t="s">
         <v>438</v>
       </c>
-      <c r="H5" s="116">
+      <c r="H5" s="39">
         <v>45084</v>
       </c>
-      <c r="I5" s="115">
+      <c r="I5">
         <v>3</v>
       </c>
       <c r="J5">
@@ -10096,31 +10790,31 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="115">
+      <c r="A6">
         <v>7</v>
       </c>
-      <c r="B6" s="115">
+      <c r="B6">
         <v>12</v>
       </c>
-      <c r="C6" s="115">
+      <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" s="115" t="s">
+      <c r="D6" t="s">
         <v>436</v>
       </c>
-      <c r="E6" s="116">
+      <c r="E6" s="39">
         <v>45566</v>
       </c>
-      <c r="F6" s="117">
+      <c r="F6" s="109">
         <v>0.5229166666666667</v>
       </c>
-      <c r="G6" s="115" t="s">
+      <c r="G6" t="s">
         <v>439</v>
       </c>
-      <c r="H6" s="116">
+      <c r="H6" s="39">
         <v>45420</v>
       </c>
-      <c r="I6" s="115" t="s">
+      <c r="I6" t="s">
         <v>438</v>
       </c>
       <c r="J6">
@@ -12028,7 +12722,7 @@
       </c>
       <c r="B100" s="19">
         <f ca="1">NOW()</f>
-        <v>45938.493500231481</v>
+        <v>46316.424889236114</v>
       </c>
       <c r="D100" s="104">
         <f ca="1">IF(ISNUMBER(B100),1,0)</f>
@@ -12718,7 +13412,7 @@
       </c>
       <c r="B144" s="18">
         <f ca="1">TODAY()</f>
-        <v>45938</v>
+        <v>46316</v>
       </c>
       <c r="D144" s="104">
         <f ca="1">IF(ISNUMBER(B144),1,0)</f>
@@ -13067,10 +13761,10 @@
       <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="D1" s="115" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="110"/>
+      <c r="E1" s="115"/>
       <c r="F1" t="s">
         <v>233</v>
       </c>
@@ -13083,8 +13777,8 @@
         <f>SUM(A1)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
       <c r="H2" t="str">
         <f>[1]Feuil1!$A$1</f>
         <v>referenced string</v>
@@ -13120,21 +13814,21 @@
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" cm="1">
         <f t="array" aca="1" ref="A30:B31" ca="1">_xlfn.RANDARRAY(2,2)</f>
-        <v>0.7272925709748963</v>
+        <v>0.78768916454204807</v>
       </c>
       <c r="B30">
         <f ca="1"/>
-        <v>0.95782684877879687</v>
+        <v>0.98576428000403649</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
         <f ca="1"/>
-        <v>0.31704384406036645</v>
+        <v>0.3036437649516297</v>
       </c>
       <c r="B31">
         <f ca="1"/>
-        <v>8.7112099778747121E-2</v>
+        <v>9.0519996913986489E-2</v>
       </c>
     </row>
   </sheetData>
@@ -13768,7 +14462,7 @@
       </c>
       <c r="B12" s="39">
         <f ca="1">TODAY()</f>
-        <v>45938</v>
+        <v>46316</v>
       </c>
       <c r="C12" s="39">
         <f>DATE(2010,10,2)</f>
